--- a/data/Fuentes de datos/Indicadores de docentes y equipos de computo/03_Estudiantes_por_docente_y_equipo_2026.xlsx
+++ b/data/Fuentes de datos/Indicadores de docentes y equipos de computo/03_Estudiantes_por_docente_y_equipo_2026.xlsx
@@ -8,15 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jorge\Documents\GOBIERNO_DE_DATOS\Data_Steward\Observatorio_de_Educación\data\Fuentes de datos\Indicadores de docentes y equipos de computo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56CA5B9B-869F-41F0-BA9A-F6E662E630BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF33C3B4-3B70-452D-9AD9-A4FDFC9D77A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resumen municipio" sheetId="1" r:id="rId1"/>
     <sheet name="Detalle por sede" sheetId="2" r:id="rId2"/>
     <sheet name="Nota técnica" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Detalle por sede'!$A$1:$E$338</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -1471,6 +1474,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E338"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="88.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -1491,2943 +1499,2943 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>176001005813</v>
+        <v>176001027001</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="C2">
-        <v>2299</v>
+        <v>1032</v>
       </c>
       <c r="D2">
-        <v>175</v>
+        <v>513</v>
       </c>
       <c r="E2">
-        <v>13.14</v>
+        <v>2.0099999999999998</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>176001017374</v>
+        <v>176001012844</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>298</v>
       </c>
       <c r="C3">
-        <v>2129</v>
+        <v>123</v>
       </c>
       <c r="D3">
-        <v>84</v>
+        <v>15</v>
       </c>
       <c r="E3">
-        <v>25.35</v>
+        <v>8.1999999999999993</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>176001001770</v>
+        <v>176001004191</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>285</v>
       </c>
       <c r="C4">
-        <v>1979</v>
+        <v>141</v>
       </c>
       <c r="D4">
-        <v>430</v>
+        <v>95</v>
       </c>
       <c r="E4">
-        <v>4.5999999999999996</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>176001800206</v>
+        <v>176001004124</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>235</v>
       </c>
       <c r="C5">
-        <v>1786</v>
+        <v>204</v>
       </c>
       <c r="D5">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E5">
-        <v>85.05</v>
+        <v>8.16</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>176001800214</v>
+        <v>176001014120</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>256</v>
       </c>
       <c r="C6">
-        <v>1621</v>
+        <v>170</v>
       </c>
       <c r="D6">
-        <v>134</v>
+        <v>20</v>
       </c>
       <c r="E6">
-        <v>12.1</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>176001016491</v>
+        <v>176001002849</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>134</v>
       </c>
       <c r="C7">
-        <v>1534</v>
+        <v>415</v>
       </c>
       <c r="D7">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="E7">
-        <v>12.17</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>176001043791</v>
+        <v>176001003870</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>307</v>
       </c>
       <c r="C8">
-        <v>1489</v>
+        <v>107</v>
       </c>
       <c r="D8">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="E8">
-        <v>29.2</v>
+        <v>7.64</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>176001028970</v>
+        <v>176001023811</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>137</v>
       </c>
       <c r="C9">
-        <v>1484</v>
+        <v>406</v>
       </c>
       <c r="D9">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="E9">
-        <v>16.670000000000002</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>176001004485</v>
+        <v>176001042409</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>204</v>
       </c>
       <c r="C10">
-        <v>1433</v>
+        <v>265</v>
       </c>
       <c r="D10">
-        <v>510</v>
+        <v>40</v>
       </c>
       <c r="E10">
-        <v>2.81</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>176001015983</v>
+        <v>176001011724</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="C11">
-        <v>1430</v>
+        <v>479</v>
       </c>
       <c r="D11">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="E11">
-        <v>24.66</v>
+        <v>5.57</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>176001004515</v>
+        <v>176001004434</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>155</v>
       </c>
       <c r="C12">
-        <v>1344</v>
+        <v>378</v>
       </c>
       <c r="D12">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E12">
-        <v>112</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>176001004531</v>
+        <v>176001004434</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>155</v>
       </c>
       <c r="C13">
-        <v>1323</v>
+        <v>378</v>
       </c>
       <c r="D13">
-        <v>110</v>
+        <v>20</v>
       </c>
       <c r="E13">
-        <v>12.03</v>
+        <v>18.899999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>176001001745</v>
+        <v>176001004302</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>153</v>
       </c>
       <c r="C14">
-        <v>1287</v>
+        <v>380</v>
       </c>
       <c r="D14">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="E14">
-        <v>35.75</v>
+        <v>42.22</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>176001013026</v>
+        <v>176001002814</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>240</v>
       </c>
       <c r="C15">
-        <v>1278</v>
+        <v>195</v>
       </c>
       <c r="D15">
-        <v>270</v>
+        <v>96</v>
       </c>
       <c r="E15">
-        <v>4.7300000000000004</v>
+        <v>2.0299999999999998</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>176001015959</v>
+        <v>276001005508</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>207</v>
       </c>
       <c r="C16">
-        <v>1245</v>
+        <v>262</v>
       </c>
       <c r="D16">
-        <v>293</v>
+        <v>54</v>
       </c>
       <c r="E16">
-        <v>4.25</v>
+        <v>4.8499999999999996</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>176001008669</v>
+        <v>176001005333</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>316</v>
       </c>
       <c r="C17">
-        <v>1243</v>
+        <v>79</v>
       </c>
       <c r="D17">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="E17">
-        <v>10.36</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>176001800401</v>
+        <v>176001007891</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>297</v>
       </c>
       <c r="C18">
-        <v>1213</v>
+        <v>123</v>
       </c>
       <c r="D18">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="E18">
-        <v>40.43</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>176001002881</v>
+        <v>176001003993</v>
       </c>
       <c r="B19" t="s">
-        <v>29</v>
+        <v>142</v>
       </c>
       <c r="C19">
-        <v>1185</v>
+        <v>393</v>
       </c>
       <c r="D19">
-        <v>437</v>
+        <v>22</v>
       </c>
       <c r="E19">
-        <v>2.71</v>
+        <v>17.86</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>176001020065</v>
+        <v>176001043987</v>
       </c>
       <c r="B20" t="s">
+        <v>142</v>
+      </c>
+      <c r="C20">
+        <v>237</v>
+      </c>
+      <c r="D20">
         <v>30</v>
       </c>
-      <c r="C20">
-        <v>1184</v>
-      </c>
-      <c r="D20">
-        <v>695</v>
-      </c>
       <c r="E20">
-        <v>1.7</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>176001015975</v>
+        <v>176001002733</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>249</v>
       </c>
       <c r="C21">
-        <v>1149</v>
+        <v>180</v>
       </c>
       <c r="D21">
-        <v>155</v>
+        <v>15</v>
       </c>
       <c r="E21">
-        <v>7.41</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>176001013310</v>
+        <v>176001003004</v>
       </c>
       <c r="B22" t="s">
-        <v>32</v>
+        <v>322</v>
       </c>
       <c r="C22">
-        <v>1135</v>
+        <v>68</v>
       </c>
       <c r="D22">
-        <v>192</v>
+        <v>5</v>
       </c>
       <c r="E22">
-        <v>5.91</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>176001025946</v>
+        <v>176001004019</v>
       </c>
       <c r="B23" t="s">
-        <v>33</v>
+        <v>245</v>
       </c>
       <c r="C23">
-        <v>1132</v>
+        <v>184</v>
       </c>
       <c r="D23">
-        <v>155</v>
+        <v>70</v>
       </c>
       <c r="E23">
-        <v>7.3</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>176001001796</v>
+        <v>176001007883</v>
       </c>
       <c r="B24" t="s">
-        <v>34</v>
+        <v>117</v>
       </c>
       <c r="C24">
-        <v>1127</v>
+        <v>466</v>
       </c>
       <c r="D24">
-        <v>134</v>
+        <v>105</v>
       </c>
       <c r="E24">
-        <v>8.41</v>
+        <v>4.4400000000000004</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>176001007166</v>
+        <v>276001005460</v>
       </c>
       <c r="B25" t="s">
-        <v>35</v>
+        <v>296</v>
       </c>
       <c r="C25">
-        <v>1061</v>
+        <v>125</v>
       </c>
       <c r="D25">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="E25">
-        <v>7.69</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>176001024273</v>
+        <v>176001042760</v>
       </c>
       <c r="B26" t="s">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="C26">
-        <v>1057</v>
+        <v>576</v>
       </c>
       <c r="D26">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="E26">
-        <v>25.17</v>
+        <v>9.44</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>176001002253</v>
+        <v>176001003128</v>
       </c>
       <c r="B27" t="s">
-        <v>37</v>
+        <v>194</v>
       </c>
       <c r="C27">
-        <v>1045</v>
+        <v>284</v>
       </c>
       <c r="D27">
-        <v>169</v>
+        <v>23</v>
       </c>
       <c r="E27">
-        <v>6.18</v>
+        <v>12.35</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>176001012089</v>
+        <v>176001004701</v>
       </c>
       <c r="B28" t="s">
-        <v>38</v>
+        <v>160</v>
       </c>
       <c r="C28">
-        <v>1041</v>
+        <v>364</v>
       </c>
       <c r="D28">
-        <v>178</v>
+        <v>88</v>
       </c>
       <c r="E28">
-        <v>5.85</v>
+        <v>4.1399999999999997</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>176001027001</v>
+        <v>176001030125</v>
       </c>
       <c r="B29" t="s">
-        <v>39</v>
+        <v>160</v>
       </c>
       <c r="C29">
-        <v>1032</v>
+        <v>14</v>
       </c>
       <c r="D29">
-        <v>513</v>
+        <v>20</v>
       </c>
       <c r="E29">
-        <v>2.0099999999999998</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>176001001818</v>
+        <v>176001004043</v>
       </c>
       <c r="B30" t="s">
-        <v>40</v>
+        <v>278</v>
       </c>
       <c r="C30">
-        <v>999</v>
+        <v>152</v>
       </c>
       <c r="D30">
-        <v>211</v>
+        <v>6</v>
       </c>
       <c r="E30">
-        <v>4.7300000000000004</v>
+        <v>25.33</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>176001030788</v>
+        <v>176001007638</v>
       </c>
       <c r="B31" t="s">
-        <v>41</v>
+        <v>299</v>
       </c>
       <c r="C31">
-        <v>968</v>
+        <v>122</v>
       </c>
       <c r="D31">
-        <v>178</v>
+        <v>119</v>
       </c>
       <c r="E31">
-        <v>5.44</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>176001005121</v>
+        <v>176001028171</v>
       </c>
       <c r="B32" t="s">
-        <v>42</v>
+        <v>175</v>
       </c>
       <c r="C32">
-        <v>966</v>
+        <v>325</v>
       </c>
       <c r="D32">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E32">
-        <v>34.5</v>
+        <v>10.83</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>176001016009</v>
+        <v>176001004868</v>
       </c>
       <c r="B33" t="s">
-        <v>43</v>
+        <v>139</v>
       </c>
       <c r="C33">
-        <v>965</v>
+        <v>401</v>
       </c>
       <c r="D33">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E33">
-        <v>21.93</v>
+        <v>10.02</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>176001007131</v>
+        <v>176001003942</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>201</v>
       </c>
       <c r="C34">
-        <v>962</v>
+        <v>268</v>
       </c>
       <c r="D34">
-        <v>170</v>
+        <v>13</v>
       </c>
       <c r="E34">
-        <v>5.66</v>
+        <v>20.62</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>176001020359</v>
+        <v>176001800231</v>
       </c>
       <c r="B35" t="s">
-        <v>45</v>
+        <v>314</v>
       </c>
       <c r="C35">
-        <v>935</v>
+        <v>94</v>
       </c>
       <c r="D35">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="E35">
-        <v>31.17</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>176001007875</v>
+        <v>176001800249</v>
       </c>
       <c r="B36" t="s">
+        <v>265</v>
+      </c>
+      <c r="C36">
+        <v>160</v>
+      </c>
+      <c r="D36">
         <v>46</v>
       </c>
-      <c r="C36">
-        <v>929</v>
-      </c>
-      <c r="D36">
-        <v>615</v>
-      </c>
       <c r="E36">
-        <v>1.51</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>176001005341</v>
+        <v>276001005141</v>
       </c>
       <c r="B37" t="s">
-        <v>47</v>
+        <v>272</v>
       </c>
       <c r="C37">
-        <v>921</v>
+        <v>156</v>
       </c>
       <c r="D37">
-        <v>170</v>
+        <v>45</v>
       </c>
       <c r="E37">
-        <v>5.42</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>176001007115</v>
+        <v>276001003394</v>
       </c>
       <c r="B38" t="s">
-        <v>48</v>
+        <v>178</v>
       </c>
       <c r="C38">
-        <v>920</v>
+        <v>320</v>
       </c>
       <c r="D38">
-        <v>136</v>
+        <v>22</v>
       </c>
       <c r="E38">
-        <v>6.76</v>
+        <v>14.55</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>176001002768</v>
+        <v>176001003080</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>337</v>
       </c>
       <c r="C39">
-        <v>879</v>
+        <v>19</v>
       </c>
       <c r="D39">
-        <v>95</v>
+        <v>18</v>
       </c>
       <c r="E39">
-        <v>9.25</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>176001001753</v>
+        <v>176001009011</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>247</v>
       </c>
       <c r="C40">
-        <v>860</v>
+        <v>184</v>
       </c>
       <c r="D40">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E40">
-        <v>37.39</v>
+        <v>5.94</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>176001022416</v>
+        <v>176001008677</v>
       </c>
       <c r="B41" t="s">
-        <v>51</v>
+        <v>310</v>
       </c>
       <c r="C41">
-        <v>859</v>
+        <v>101</v>
       </c>
       <c r="D41">
-        <v>214</v>
+        <v>11</v>
       </c>
       <c r="E41">
-        <v>4.01</v>
+        <v>9.18</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>176001032055</v>
+        <v>176001003918</v>
       </c>
       <c r="B42" t="s">
-        <v>52</v>
+        <v>165</v>
       </c>
       <c r="C42">
-        <v>851</v>
+        <v>357</v>
       </c>
       <c r="D42">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="E42">
-        <v>12.7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>176001020693</v>
+        <v>176001004116</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>251</v>
       </c>
       <c r="C43">
-        <v>848</v>
+        <v>177</v>
       </c>
       <c r="D43">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="E43">
-        <v>18.84</v>
+        <v>13.62</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>176001001664</v>
+        <v>176001025661</v>
       </c>
       <c r="B44" t="s">
-        <v>54</v>
+        <v>111</v>
       </c>
       <c r="C44">
-        <v>846</v>
+        <v>483</v>
       </c>
       <c r="D44">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="E44">
-        <v>10.58</v>
+        <v>15.09</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>176001004221</v>
+        <v>276001003271</v>
       </c>
       <c r="B45" t="s">
-        <v>55</v>
+        <v>338</v>
       </c>
       <c r="C45">
-        <v>845</v>
+        <v>14</v>
       </c>
       <c r="D45">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E45">
-        <v>49.71</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>176001003161</v>
+        <v>176001003896</v>
       </c>
       <c r="B46" t="s">
-        <v>56</v>
+        <v>268</v>
       </c>
       <c r="C46">
-        <v>833</v>
+        <v>157</v>
       </c>
       <c r="D46">
-        <v>291</v>
+        <v>14</v>
       </c>
       <c r="E46">
-        <v>2.86</v>
+        <v>11.21</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>176001029411</v>
+        <v>176001005031</v>
       </c>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>193</v>
       </c>
       <c r="C47">
-        <v>831</v>
+        <v>290</v>
       </c>
       <c r="D47">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E47">
-        <v>41.55</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>176001014359</v>
+        <v>176001004850</v>
       </c>
       <c r="B48" t="s">
-        <v>58</v>
+        <v>181</v>
       </c>
       <c r="C48">
-        <v>820</v>
+        <v>312</v>
       </c>
       <c r="D48">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E48">
-        <v>20.5</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>176001005805</v>
+        <v>276001043884</v>
       </c>
       <c r="B49" t="s">
-        <v>59</v>
+        <v>104</v>
       </c>
       <c r="C49">
-        <v>815</v>
+        <v>508</v>
       </c>
       <c r="D49">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="E49">
-        <v>14.55</v>
+        <v>14.51</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>176001004256</v>
+        <v>176001003934</v>
       </c>
       <c r="B50" t="s">
-        <v>60</v>
+        <v>302</v>
       </c>
       <c r="C50">
-        <v>808</v>
+        <v>119</v>
       </c>
       <c r="D50">
-        <v>60</v>
+        <v>109</v>
       </c>
       <c r="E50">
-        <v>13.47</v>
+        <v>1.0900000000000001</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>176001012976</v>
+        <v>176001004221</v>
       </c>
       <c r="B51" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C51">
-        <v>800</v>
+        <v>845</v>
       </c>
       <c r="D51">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="E51">
-        <v>16</v>
+        <v>49.71</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>376001017608</v>
+        <v>176001025849</v>
       </c>
       <c r="B52" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="C52">
-        <v>797</v>
+        <v>535</v>
       </c>
       <c r="D52">
-        <v>139</v>
+        <v>63</v>
       </c>
       <c r="E52">
-        <v>5.73</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>176001002555</v>
+        <v>176001002768</v>
       </c>
       <c r="B53" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="C53">
-        <v>773</v>
+        <v>879</v>
       </c>
       <c r="D53">
-        <v>190</v>
+        <v>95</v>
       </c>
       <c r="E53">
-        <v>4.07</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>176001040119</v>
+        <v>176001800036</v>
       </c>
       <c r="B54" t="s">
-        <v>64</v>
+        <v>271</v>
       </c>
       <c r="C54">
-        <v>764</v>
+        <v>156</v>
       </c>
       <c r="D54">
-        <v>74</v>
+        <v>16</v>
       </c>
       <c r="E54">
-        <v>10.32</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>176001013018</v>
+        <v>176001002873</v>
       </c>
       <c r="B55" t="s">
-        <v>65</v>
+        <v>279</v>
       </c>
       <c r="C55">
-        <v>764</v>
+        <v>151</v>
       </c>
       <c r="D55">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E55">
-        <v>25.47</v>
+        <v>10.07</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>176001006356</v>
+        <v>176001003861</v>
       </c>
       <c r="B56" t="s">
-        <v>66</v>
+        <v>305</v>
       </c>
       <c r="C56">
-        <v>757</v>
+        <v>115</v>
       </c>
       <c r="D56">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="E56">
-        <v>11.65</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>176001003888</v>
+        <v>176001002822</v>
       </c>
       <c r="B57" t="s">
-        <v>67</v>
+        <v>239</v>
       </c>
       <c r="C57">
-        <v>754</v>
+        <v>195</v>
       </c>
       <c r="D57">
-        <v>145</v>
+        <v>10</v>
       </c>
       <c r="E57">
-        <v>5.2</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>176001032063</v>
+        <v>176001004922</v>
       </c>
       <c r="B58" t="s">
-        <v>68</v>
+        <v>152</v>
       </c>
       <c r="C58">
-        <v>752</v>
+        <v>385</v>
       </c>
       <c r="D58">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E58">
-        <v>32.700000000000003</v>
+        <v>12.83</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>176001002792</v>
+        <v>176001002776</v>
       </c>
       <c r="B59" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="C59">
-        <v>750</v>
+        <v>548</v>
       </c>
       <c r="D59">
-        <v>498</v>
+        <v>12</v>
       </c>
       <c r="E59">
-        <v>1.51</v>
+        <v>45.67</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>176001012101</v>
+        <v>176001004591</v>
       </c>
       <c r="B60" t="s">
-        <v>70</v>
+        <v>275</v>
       </c>
       <c r="C60">
-        <v>741</v>
+        <v>154</v>
       </c>
       <c r="D60">
-        <v>145</v>
+        <v>26</v>
       </c>
       <c r="E60">
-        <v>5.1100000000000003</v>
+        <v>5.92</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>176001009045</v>
+        <v>276001005524</v>
       </c>
       <c r="B61" t="s">
-        <v>71</v>
+        <v>275</v>
       </c>
       <c r="C61">
-        <v>730</v>
+        <v>30</v>
       </c>
       <c r="D61">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="E61">
-        <v>18.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>176001008723</v>
+        <v>276001007641</v>
       </c>
       <c r="B62" t="s">
-        <v>72</v>
+        <v>293</v>
       </c>
       <c r="C62">
-        <v>707</v>
+        <v>130</v>
       </c>
       <c r="D62">
-        <v>170</v>
+        <v>83</v>
       </c>
       <c r="E62">
-        <v>4.16</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>176001028872</v>
+        <v>176001003373</v>
       </c>
       <c r="B63" t="s">
-        <v>73</v>
+        <v>184</v>
       </c>
       <c r="C63">
-        <v>703</v>
+        <v>306</v>
       </c>
       <c r="D63">
-        <v>511</v>
+        <v>139</v>
       </c>
       <c r="E63">
-        <v>1.38</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>176001030117</v>
+        <v>176001004451</v>
       </c>
       <c r="B64" t="s">
-        <v>74</v>
+        <v>258</v>
       </c>
       <c r="C64">
-        <v>703</v>
+        <v>170</v>
       </c>
       <c r="D64">
-        <v>275</v>
+        <v>149</v>
       </c>
       <c r="E64">
-        <v>2.56</v>
+        <v>1.1399999999999999</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>176001003055</v>
+        <v>176001004108</v>
       </c>
       <c r="B65" t="s">
-        <v>75</v>
+        <v>121</v>
       </c>
       <c r="C65">
-        <v>694</v>
+        <v>455</v>
       </c>
       <c r="D65">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="E65">
-        <v>7.23</v>
+        <v>15.17</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>176001001729</v>
+        <v>176001002890</v>
       </c>
       <c r="B66" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="C66">
-        <v>690</v>
+        <v>529</v>
       </c>
       <c r="D66">
-        <v>257</v>
+        <v>28</v>
       </c>
       <c r="E66">
-        <v>2.68</v>
+        <v>18.89</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>176001001672</v>
+        <v>176001003969</v>
       </c>
       <c r="B67" t="s">
-        <v>77</v>
+        <v>147</v>
       </c>
       <c r="C67">
-        <v>690</v>
+        <v>389</v>
       </c>
       <c r="D67">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="E67">
-        <v>9.86</v>
+        <v>22.88</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>176001001729</v>
+        <v>176001002938</v>
       </c>
       <c r="B68" t="s">
-        <v>76</v>
+        <v>195</v>
       </c>
       <c r="C68">
-        <v>690</v>
+        <v>281</v>
       </c>
       <c r="D68">
-        <v>188</v>
+        <v>293</v>
       </c>
       <c r="E68">
-        <v>3.67</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>176001006445</v>
+        <v>176001004876</v>
       </c>
       <c r="B69" t="s">
-        <v>78</v>
+        <v>244</v>
       </c>
       <c r="C69">
-        <v>689</v>
+        <v>184</v>
       </c>
       <c r="D69">
-        <v>44</v>
+        <v>309</v>
       </c>
       <c r="E69">
-        <v>15.66</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>176001022441</v>
+        <v>176001004710</v>
       </c>
       <c r="B70" t="s">
-        <v>79</v>
+        <v>267</v>
       </c>
       <c r="C70">
-        <v>642</v>
+        <v>159</v>
       </c>
       <c r="D70">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="E70">
-        <v>8.02</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>176001030478</v>
+        <v>176001004469</v>
       </c>
       <c r="B71" t="s">
-        <v>80</v>
+        <v>248</v>
       </c>
       <c r="C71">
-        <v>632</v>
+        <v>183</v>
       </c>
       <c r="D71">
-        <v>431</v>
+        <v>26</v>
       </c>
       <c r="E71">
-        <v>1.47</v>
+        <v>7.04</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>176001003411</v>
+        <v>176001004264</v>
       </c>
       <c r="B72" t="s">
-        <v>81</v>
+        <v>230</v>
       </c>
       <c r="C72">
-        <v>628</v>
+        <v>212</v>
       </c>
       <c r="D72">
-        <v>22</v>
+        <v>113</v>
       </c>
       <c r="E72">
-        <v>28.55</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>376001017438</v>
+        <v>276001800481</v>
       </c>
       <c r="B73" t="s">
-        <v>82</v>
+        <v>260</v>
       </c>
       <c r="C73">
-        <v>625</v>
+        <v>166</v>
       </c>
       <c r="D73">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E73">
-        <v>15.62</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>176001005074</v>
+        <v>176001004728</v>
       </c>
       <c r="B74" t="s">
-        <v>83</v>
+        <v>161</v>
       </c>
       <c r="C74">
-        <v>624</v>
+        <v>364</v>
       </c>
       <c r="D74">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="E74">
-        <v>18.91</v>
+        <v>8.09</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>276001003289</v>
+        <v>276001005150</v>
       </c>
       <c r="B75" t="s">
-        <v>84</v>
+        <v>324</v>
       </c>
       <c r="C75">
-        <v>622</v>
+        <v>67</v>
       </c>
       <c r="D75">
-        <v>50</v>
+        <v>107</v>
       </c>
       <c r="E75">
-        <v>12.44</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>176001001800</v>
+        <v>176001004078</v>
       </c>
       <c r="B76" t="s">
-        <v>85</v>
+        <v>209</v>
       </c>
       <c r="C76">
-        <v>609</v>
+        <v>258</v>
       </c>
       <c r="D76">
-        <v>86</v>
+        <v>119</v>
       </c>
       <c r="E76">
-        <v>7.08</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>176001003403</v>
+        <v>176001015991</v>
       </c>
       <c r="B77" t="s">
-        <v>86</v>
+        <v>141</v>
       </c>
       <c r="C77">
-        <v>597</v>
+        <v>393</v>
       </c>
       <c r="D77">
-        <v>94</v>
+        <v>150</v>
       </c>
       <c r="E77">
-        <v>6.35</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>176001003586</v>
+        <v>176001008669</v>
       </c>
       <c r="B78" t="s">
-        <v>87</v>
+        <v>27</v>
       </c>
       <c r="C78">
-        <v>591</v>
+        <v>1243</v>
       </c>
       <c r="D78">
-        <v>484</v>
+        <v>120</v>
       </c>
       <c r="E78">
-        <v>1.22</v>
+        <v>10.36</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>176001005015</v>
+        <v>176001029411</v>
       </c>
       <c r="B79" t="s">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="C79">
-        <v>591</v>
+        <v>831</v>
       </c>
       <c r="D79">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="E79">
-        <v>12.57</v>
+        <v>41.55</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>176001004990</v>
+        <v>176001001681</v>
       </c>
       <c r="B80" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="C80">
-        <v>585</v>
+        <v>501</v>
       </c>
       <c r="D80">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E80">
-        <v>16.25</v>
+        <v>12.52</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>176001042760</v>
+        <v>176001040101</v>
       </c>
       <c r="B81" t="s">
-        <v>90</v>
+        <v>138</v>
       </c>
       <c r="C81">
-        <v>576</v>
+        <v>401</v>
       </c>
       <c r="D81">
-        <v>61</v>
+        <v>186</v>
       </c>
       <c r="E81">
-        <v>9.44</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>176001005082</v>
+        <v>176001011163</v>
       </c>
       <c r="B82" t="s">
-        <v>91</v>
+        <v>127</v>
       </c>
       <c r="C82">
-        <v>570</v>
+        <v>438</v>
       </c>
       <c r="D82">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="E82">
-        <v>14.25</v>
+        <v>6.08</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>176001003951</v>
+        <v>176001003161</v>
       </c>
       <c r="B83" t="s">
-        <v>92</v>
+        <v>56</v>
       </c>
       <c r="C83">
-        <v>568</v>
+        <v>833</v>
       </c>
       <c r="D83">
-        <v>50</v>
+        <v>291</v>
       </c>
       <c r="E83">
-        <v>11.36</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>276001011354</v>
+        <v>176001008791</v>
       </c>
       <c r="B84" t="s">
-        <v>93</v>
+        <v>241</v>
       </c>
       <c r="C84">
-        <v>561</v>
+        <v>195</v>
       </c>
       <c r="D84">
-        <v>134</v>
+        <v>24</v>
       </c>
       <c r="E84">
-        <v>4.1900000000000004</v>
+        <v>8.1199999999999992</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>176001005023</v>
+        <v>176001008642</v>
       </c>
       <c r="B85" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="C85">
-        <v>559</v>
+        <v>471</v>
       </c>
       <c r="D85">
-        <v>35</v>
+        <v>108</v>
       </c>
       <c r="E85">
-        <v>15.97</v>
+        <v>4.3600000000000003</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>176001004272</v>
+        <v>176001007131</v>
       </c>
       <c r="B86" t="s">
-        <v>95</v>
+        <v>44</v>
       </c>
       <c r="C86">
-        <v>555</v>
+        <v>962</v>
       </c>
       <c r="D86">
-        <v>32</v>
+        <v>170</v>
       </c>
       <c r="E86">
-        <v>17.34</v>
+        <v>5.66</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>176001012798</v>
+        <v>176001020065</v>
       </c>
       <c r="B87" t="s">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="C87">
-        <v>549</v>
+        <v>1184</v>
       </c>
       <c r="D87">
-        <v>283</v>
+        <v>695</v>
       </c>
       <c r="E87">
-        <v>1.94</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>176001002776</v>
+        <v>176001015975</v>
       </c>
       <c r="B88" t="s">
-        <v>97</v>
+        <v>31</v>
       </c>
       <c r="C88">
-        <v>548</v>
+        <v>1149</v>
       </c>
       <c r="D88">
-        <v>12</v>
+        <v>155</v>
       </c>
       <c r="E88">
-        <v>45.67</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>176001001699</v>
+        <v>176001005805</v>
       </c>
       <c r="B89" t="s">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="C89">
-        <v>538</v>
+        <v>815</v>
       </c>
       <c r="D89">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="E89">
-        <v>6.99</v>
+        <v>14.55</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>176001006461</v>
+        <v>176001004256</v>
       </c>
       <c r="B90" t="s">
-        <v>99</v>
+        <v>60</v>
       </c>
       <c r="C90">
-        <v>536</v>
+        <v>808</v>
       </c>
       <c r="D90">
-        <v>222</v>
+        <v>60</v>
       </c>
       <c r="E90">
-        <v>2.41</v>
+        <v>13.47</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>176001025849</v>
+        <v>176001001818</v>
       </c>
       <c r="B91" t="s">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="C91">
-        <v>535</v>
+        <v>999</v>
       </c>
       <c r="D91">
-        <v>63</v>
+        <v>211</v>
       </c>
       <c r="E91">
-        <v>8.49</v>
+        <v>4.7300000000000004</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>176001002890</v>
+        <v>176001007115</v>
       </c>
       <c r="B92" t="s">
-        <v>101</v>
+        <v>48</v>
       </c>
       <c r="C92">
-        <v>529</v>
+        <v>920</v>
       </c>
       <c r="D92">
-        <v>28</v>
+        <v>136</v>
       </c>
       <c r="E92">
-        <v>18.89</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>176001037600</v>
+        <v>276001004889</v>
       </c>
       <c r="B93" t="s">
-        <v>102</v>
+        <v>146</v>
       </c>
       <c r="C93">
-        <v>524</v>
+        <v>391</v>
       </c>
       <c r="D93">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="E93">
-        <v>2.1</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>176001001702</v>
+        <v>176001001770</v>
       </c>
       <c r="B94" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="C94">
-        <v>521</v>
+        <v>1979</v>
       </c>
       <c r="D94">
-        <v>73</v>
+        <v>430</v>
       </c>
       <c r="E94">
-        <v>7.14</v>
+        <v>4.5999999999999996</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>276001043884</v>
+        <v>176001002911</v>
       </c>
       <c r="B95" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="C95">
-        <v>508</v>
+        <v>408</v>
       </c>
       <c r="D95">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E95">
-        <v>14.51</v>
+        <v>10.46</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>176001002920</v>
+        <v>176001004329</v>
       </c>
       <c r="B96" t="s">
-        <v>105</v>
+        <v>148</v>
       </c>
       <c r="C96">
-        <v>501</v>
+        <v>387</v>
       </c>
       <c r="D96">
-        <v>135</v>
+        <v>10</v>
       </c>
       <c r="E96">
-        <v>3.71</v>
+        <v>38.700000000000003</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>176001001681</v>
+        <v>276001010994</v>
       </c>
       <c r="B97" t="s">
-        <v>106</v>
+        <v>164</v>
       </c>
       <c r="C97">
-        <v>501</v>
+        <v>358</v>
       </c>
       <c r="D97">
-        <v>40</v>
+        <v>238</v>
       </c>
       <c r="E97">
-        <v>12.52</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>176001002806</v>
+        <v>176001017374</v>
       </c>
       <c r="B98" t="s">
-        <v>107</v>
+        <v>13</v>
       </c>
       <c r="C98">
-        <v>489</v>
+        <v>2129</v>
       </c>
       <c r="D98">
-        <v>455</v>
+        <v>84</v>
       </c>
       <c r="E98">
-        <v>1.07</v>
+        <v>25.35</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>176001004914</v>
+        <v>176001001702</v>
       </c>
       <c r="B99" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C99">
-        <v>488</v>
+        <v>521</v>
       </c>
       <c r="D99">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="E99">
-        <v>15.25</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>176001003225</v>
+        <v>176001006119</v>
       </c>
       <c r="B100" t="s">
-        <v>109</v>
+        <v>208</v>
       </c>
       <c r="C100">
-        <v>486</v>
+        <v>261</v>
       </c>
       <c r="D100">
-        <v>42</v>
+        <v>297</v>
       </c>
       <c r="E100">
-        <v>11.57</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>176001003195</v>
+        <v>176001800206</v>
       </c>
       <c r="B101" t="s">
-        <v>110</v>
+        <v>15</v>
       </c>
       <c r="C101">
-        <v>485</v>
+        <v>1786</v>
       </c>
       <c r="D101">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="E101">
-        <v>9.6999999999999993</v>
+        <v>85.05</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>176001025661</v>
+        <v>276001022232</v>
       </c>
       <c r="B102" t="s">
-        <v>111</v>
+        <v>188</v>
       </c>
       <c r="C102">
-        <v>483</v>
+        <v>298</v>
       </c>
       <c r="D102">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E102">
-        <v>15.09</v>
+        <v>9.93</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>176001011724</v>
+        <v>176001001656</v>
       </c>
       <c r="B103" t="s">
-        <v>112</v>
+        <v>233</v>
       </c>
       <c r="C103">
-        <v>479</v>
+        <v>208</v>
       </c>
       <c r="D103">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="E103">
-        <v>5.57</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>176001003012</v>
+        <v>176001020693</v>
       </c>
       <c r="B104" t="s">
-        <v>113</v>
+        <v>53</v>
       </c>
       <c r="C104">
-        <v>477</v>
+        <v>848</v>
       </c>
       <c r="D104">
-        <v>372</v>
+        <v>45</v>
       </c>
       <c r="E104">
-        <v>1.28</v>
+        <v>18.84</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>176001004655</v>
+        <v>176001005813</v>
       </c>
       <c r="B105" t="s">
-        <v>114</v>
+        <v>12</v>
       </c>
       <c r="C105">
-        <v>476</v>
+        <v>2299</v>
       </c>
       <c r="D105">
-        <v>40</v>
+        <v>175</v>
       </c>
       <c r="E105">
-        <v>11.9</v>
+        <v>13.14</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>176001008642</v>
+        <v>176001004973</v>
       </c>
       <c r="B106" t="s">
-        <v>115</v>
+        <v>300</v>
       </c>
       <c r="C106">
-        <v>471</v>
+        <v>122</v>
       </c>
       <c r="D106">
-        <v>108</v>
+        <v>20</v>
       </c>
       <c r="E106">
-        <v>4.3600000000000003</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>276001005184</v>
+        <v>176001024273</v>
       </c>
       <c r="B107" t="s">
-        <v>116</v>
+        <v>36</v>
       </c>
       <c r="C107">
-        <v>467</v>
+        <v>1057</v>
       </c>
       <c r="D107">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="E107">
-        <v>6.67</v>
+        <v>25.17</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>176001007883</v>
+        <v>176001005716</v>
       </c>
       <c r="B108" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="C108">
-        <v>466</v>
+        <v>399</v>
       </c>
       <c r="D108">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="E108">
-        <v>4.4400000000000004</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>176001014138</v>
+        <v>176001003195</v>
       </c>
       <c r="B109" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C109">
-        <v>466</v>
+        <v>485</v>
       </c>
       <c r="D109">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="E109">
-        <v>6.66</v>
+        <v>9.6999999999999993</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>176001025962</v>
+        <v>176001001826</v>
       </c>
       <c r="B110" t="s">
-        <v>119</v>
+        <v>169</v>
       </c>
       <c r="C110">
-        <v>461</v>
+        <v>345</v>
       </c>
       <c r="D110">
-        <v>71</v>
+        <v>532</v>
       </c>
       <c r="E110">
-        <v>6.49</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>276001025452</v>
+        <v>176001003586</v>
       </c>
       <c r="B111" t="s">
-        <v>120</v>
+        <v>87</v>
       </c>
       <c r="C111">
-        <v>457</v>
+        <v>591</v>
       </c>
       <c r="D111">
-        <v>30</v>
+        <v>484</v>
       </c>
       <c r="E111">
-        <v>15.23</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>176001004108</v>
+        <v>176001012101</v>
       </c>
       <c r="B112" t="s">
-        <v>121</v>
+        <v>70</v>
       </c>
       <c r="C112">
-        <v>455</v>
+        <v>741</v>
       </c>
       <c r="D112">
-        <v>30</v>
+        <v>145</v>
       </c>
       <c r="E112">
-        <v>15.17</v>
+        <v>5.1100000000000003</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>176001004230</v>
+        <v>176001004485</v>
       </c>
       <c r="B113" t="s">
-        <v>122</v>
+        <v>20</v>
       </c>
       <c r="C113">
-        <v>455</v>
+        <v>1433</v>
       </c>
       <c r="D113">
-        <v>254</v>
+        <v>510</v>
       </c>
       <c r="E113">
-        <v>1.79</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>176001004060</v>
+        <v>176001003951</v>
       </c>
       <c r="B114" t="s">
-        <v>123</v>
+        <v>92</v>
       </c>
       <c r="C114">
-        <v>453</v>
+        <v>568</v>
       </c>
       <c r="D114">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="E114">
-        <v>16.18</v>
+        <v>11.36</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>176001042280</v>
+        <v>176001014359</v>
       </c>
       <c r="B115" t="s">
-        <v>124</v>
+        <v>58</v>
       </c>
       <c r="C115">
-        <v>452</v>
+        <v>820</v>
       </c>
       <c r="D115">
-        <v>102</v>
+        <v>40</v>
       </c>
       <c r="E115">
-        <v>4.43</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>176001022360</v>
+        <v>276001005184</v>
       </c>
       <c r="B116" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="C116">
-        <v>448</v>
+        <v>467</v>
       </c>
       <c r="D116">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="E116">
-        <v>11.79</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>176001800419</v>
+        <v>176001014138</v>
       </c>
       <c r="B117" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C117">
-        <v>446</v>
+        <v>466</v>
       </c>
       <c r="D117">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="E117">
-        <v>10.62</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>176001011163</v>
+        <v>476001020719</v>
       </c>
       <c r="B118" t="s">
-        <v>127</v>
+        <v>282</v>
       </c>
       <c r="C118">
-        <v>438</v>
+        <v>148</v>
       </c>
       <c r="D118">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="E118">
-        <v>6.08</v>
+        <v>5.48</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>176001003837</v>
+        <v>176001001699</v>
       </c>
       <c r="B119" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="C119">
-        <v>438</v>
+        <v>538</v>
       </c>
       <c r="D119">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="E119">
-        <v>12.51</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>176001006470</v>
+        <v>276001042756</v>
       </c>
       <c r="B120" t="s">
-        <v>129</v>
+        <v>323</v>
       </c>
       <c r="C120">
-        <v>433</v>
+        <v>68</v>
       </c>
       <c r="D120">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="E120">
-        <v>8.33</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>176001800061</v>
+        <v>176001006356</v>
       </c>
       <c r="B121" t="s">
-        <v>130</v>
+        <v>66</v>
       </c>
       <c r="C121">
-        <v>424</v>
+        <v>757</v>
       </c>
       <c r="D121">
-        <v>6</v>
+        <v>65</v>
       </c>
       <c r="E121">
-        <v>70.67</v>
+        <v>11.65</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>176001004094</v>
+        <v>176001001745</v>
       </c>
       <c r="B122" t="s">
-        <v>131</v>
+        <v>24</v>
       </c>
       <c r="C122">
-        <v>421</v>
+        <v>1287</v>
       </c>
       <c r="D122">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="E122">
-        <v>23.39</v>
+        <v>35.75</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>276001800260</v>
+        <v>176001008766</v>
       </c>
       <c r="B123" t="s">
-        <v>132</v>
+        <v>226</v>
       </c>
       <c r="C123">
-        <v>419</v>
+        <v>227</v>
       </c>
       <c r="D123">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="E123">
-        <v>5.66</v>
+        <v>5.68</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>176001007905</v>
+        <v>176001008723</v>
       </c>
       <c r="B124" t="s">
-        <v>133</v>
+        <v>72</v>
       </c>
       <c r="C124">
-        <v>415</v>
+        <v>707</v>
       </c>
       <c r="D124">
-        <v>31</v>
+        <v>170</v>
       </c>
       <c r="E124">
-        <v>13.39</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>176001002849</v>
+        <v>176001002989</v>
       </c>
       <c r="B125" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="C125">
-        <v>415</v>
+        <v>385</v>
       </c>
       <c r="D125">
-        <v>116</v>
+        <v>160</v>
       </c>
       <c r="E125">
-        <v>3.58</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>176001004248</v>
+        <v>276001011354</v>
       </c>
       <c r="B126" t="s">
-        <v>135</v>
+        <v>93</v>
       </c>
       <c r="C126">
-        <v>409</v>
+        <v>561</v>
       </c>
       <c r="D126">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="E126">
-        <v>3.68</v>
+        <v>4.1900000000000004</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>176001002911</v>
+        <v>276001003289</v>
       </c>
       <c r="B127" t="s">
-        <v>136</v>
+        <v>84</v>
       </c>
       <c r="C127">
-        <v>408</v>
+        <v>622</v>
       </c>
       <c r="D127">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="E127">
-        <v>10.46</v>
+        <v>12.44</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>176001023811</v>
+        <v>176001002253</v>
       </c>
       <c r="B128" t="s">
-        <v>137</v>
+        <v>37</v>
       </c>
       <c r="C128">
-        <v>406</v>
+        <v>1045</v>
       </c>
       <c r="D128">
-        <v>71</v>
+        <v>169</v>
       </c>
       <c r="E128">
-        <v>5.72</v>
+        <v>6.18</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>176001040101</v>
+        <v>176001004531</v>
       </c>
       <c r="B129" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="C129">
-        <v>401</v>
+        <v>1323</v>
       </c>
       <c r="D129">
-        <v>186</v>
+        <v>110</v>
       </c>
       <c r="E129">
-        <v>2.16</v>
+        <v>12.03</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>176001004868</v>
+        <v>176001043791</v>
       </c>
       <c r="B130" t="s">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="C130">
-        <v>401</v>
+        <v>1489</v>
       </c>
       <c r="D130">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="E130">
-        <v>10.02</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131">
-        <v>176001005716</v>
+        <v>276001008574</v>
       </c>
       <c r="B131" t="s">
-        <v>140</v>
+        <v>288</v>
       </c>
       <c r="C131">
-        <v>399</v>
+        <v>135</v>
       </c>
       <c r="D131">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="E131">
-        <v>3.07</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132">
-        <v>176001015991</v>
+        <v>176001013310</v>
       </c>
       <c r="B132" t="s">
-        <v>141</v>
+        <v>32</v>
       </c>
       <c r="C132">
-        <v>393</v>
+        <v>1135</v>
       </c>
       <c r="D132">
-        <v>150</v>
+        <v>192</v>
       </c>
       <c r="E132">
-        <v>2.62</v>
+        <v>5.91</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133">
-        <v>176001003993</v>
+        <v>176001020359</v>
       </c>
       <c r="B133" t="s">
-        <v>142</v>
+        <v>45</v>
       </c>
       <c r="C133">
-        <v>393</v>
+        <v>935</v>
       </c>
       <c r="D133">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E133">
-        <v>17.86</v>
+        <v>31.17</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>276001005877</v>
+        <v>176001005368</v>
       </c>
       <c r="B134" t="s">
-        <v>143</v>
+        <v>190</v>
       </c>
       <c r="C134">
-        <v>392</v>
+        <v>297</v>
       </c>
       <c r="D134">
-        <v>137</v>
+        <v>20</v>
       </c>
       <c r="E134">
-        <v>2.86</v>
+        <v>14.85</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135">
-        <v>176001002962</v>
+        <v>176001005091</v>
       </c>
       <c r="B135" t="s">
-        <v>144</v>
+        <v>217</v>
       </c>
       <c r="C135">
-        <v>392</v>
+        <v>244</v>
       </c>
       <c r="D135">
         <v>80</v>
       </c>
       <c r="E135">
-        <v>4.9000000000000004</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136">
-        <v>176001004671</v>
+        <v>176001040119</v>
       </c>
       <c r="B136" t="s">
-        <v>145</v>
+        <v>64</v>
       </c>
       <c r="C136">
-        <v>391</v>
+        <v>764</v>
       </c>
       <c r="D136">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="E136">
-        <v>24.44</v>
+        <v>10.32</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137">
-        <v>276001004889</v>
+        <v>176001006071</v>
       </c>
       <c r="B137" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C137">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="D137">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="E137">
-        <v>2.61</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138">
-        <v>176001003969</v>
+        <v>176001025946</v>
       </c>
       <c r="B138" t="s">
-        <v>147</v>
+        <v>33</v>
       </c>
       <c r="C138">
-        <v>389</v>
+        <v>1132</v>
       </c>
       <c r="D138">
-        <v>17</v>
+        <v>155</v>
       </c>
       <c r="E138">
-        <v>22.88</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139">
-        <v>176001004329</v>
+        <v>176001040079</v>
       </c>
       <c r="B139" t="s">
-        <v>148</v>
+        <v>210</v>
       </c>
       <c r="C139">
-        <v>387</v>
+        <v>258</v>
       </c>
       <c r="D139">
-        <v>10</v>
+        <v>181</v>
       </c>
       <c r="E139">
-        <v>38.700000000000003</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140">
-        <v>176001006071</v>
+        <v>176001005341</v>
       </c>
       <c r="B140" t="s">
-        <v>149</v>
+        <v>47</v>
       </c>
       <c r="C140">
-        <v>386</v>
+        <v>921</v>
       </c>
       <c r="D140">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="E140">
-        <v>2.86</v>
+        <v>5.42</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141">
-        <v>176001015941</v>
+        <v>176001030788</v>
       </c>
       <c r="B141" t="s">
-        <v>150</v>
+        <v>41</v>
       </c>
       <c r="C141">
-        <v>385</v>
+        <v>968</v>
       </c>
       <c r="D141">
-        <v>107</v>
+        <v>178</v>
       </c>
       <c r="E141">
-        <v>3.6</v>
+        <v>5.44</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142">
-        <v>176001002989</v>
+        <v>176001002555</v>
       </c>
       <c r="B142" t="s">
-        <v>151</v>
+        <v>63</v>
       </c>
       <c r="C142">
-        <v>385</v>
+        <v>773</v>
       </c>
       <c r="D142">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="E142">
-        <v>2.41</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143">
-        <v>176001004922</v>
+        <v>176001022360</v>
       </c>
       <c r="B143" t="s">
-        <v>152</v>
+        <v>125</v>
       </c>
       <c r="C143">
-        <v>385</v>
+        <v>448</v>
       </c>
       <c r="D143">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E143">
-        <v>12.83</v>
+        <v>11.79</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144">
-        <v>176001004302</v>
+        <v>176001013301</v>
       </c>
       <c r="B144" t="s">
-        <v>153</v>
+        <v>206</v>
       </c>
       <c r="C144">
-        <v>380</v>
+        <v>264</v>
       </c>
       <c r="D144">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="E144">
-        <v>42.22</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145">
-        <v>176001006496</v>
+        <v>176001001729</v>
       </c>
       <c r="B145" t="s">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="C145">
-        <v>380</v>
+        <v>690</v>
       </c>
       <c r="D145">
-        <v>80</v>
+        <v>257</v>
       </c>
       <c r="E145">
-        <v>4.75</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146">
-        <v>176001004434</v>
+        <v>176001001729</v>
       </c>
       <c r="B146" t="s">
-        <v>155</v>
+        <v>76</v>
       </c>
       <c r="C146">
-        <v>378</v>
+        <v>690</v>
       </c>
       <c r="D146">
-        <v>21</v>
+        <v>188</v>
       </c>
       <c r="E146">
-        <v>18</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147">
-        <v>176001004434</v>
+        <v>176001016491</v>
       </c>
       <c r="B147" t="s">
-        <v>155</v>
+        <v>17</v>
       </c>
       <c r="C147">
-        <v>378</v>
+        <v>1534</v>
       </c>
       <c r="D147">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="E147">
-        <v>18.899999999999999</v>
+        <v>12.17</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148">
-        <v>176001007336</v>
+        <v>176001001753</v>
       </c>
       <c r="B148" t="s">
-        <v>156</v>
+        <v>50</v>
       </c>
       <c r="C148">
-        <v>372</v>
+        <v>860</v>
       </c>
       <c r="D148">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="E148">
-        <v>10.33</v>
+        <v>37.39</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149">
-        <v>176001004507</v>
+        <v>176001001796</v>
       </c>
       <c r="B149" t="s">
-        <v>157</v>
+        <v>34</v>
       </c>
       <c r="C149">
-        <v>371</v>
+        <v>1127</v>
       </c>
       <c r="D149">
-        <v>40</v>
+        <v>134</v>
       </c>
       <c r="E149">
-        <v>9.2799999999999994</v>
+        <v>8.41</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150">
-        <v>176001004281</v>
+        <v>176001005121</v>
       </c>
       <c r="B150" t="s">
-        <v>158</v>
+        <v>42</v>
       </c>
       <c r="C150">
-        <v>369</v>
+        <v>966</v>
       </c>
       <c r="D150">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E150">
-        <v>9</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151">
-        <v>176001022572</v>
+        <v>176001001672</v>
       </c>
       <c r="B151" t="s">
-        <v>159</v>
+        <v>77</v>
       </c>
       <c r="C151">
-        <v>368</v>
+        <v>690</v>
       </c>
       <c r="D151">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="E151">
-        <v>9.1999999999999993</v>
+        <v>9.86</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152">
-        <v>176001004701</v>
+        <v>176001037600</v>
       </c>
       <c r="B152" t="s">
-        <v>160</v>
+        <v>102</v>
       </c>
       <c r="C152">
-        <v>364</v>
+        <v>524</v>
       </c>
       <c r="D152">
-        <v>88</v>
+        <v>250</v>
       </c>
       <c r="E152">
-        <v>4.1399999999999997</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153">
-        <v>176001004728</v>
+        <v>176001028872</v>
       </c>
       <c r="B153" t="s">
-        <v>161</v>
+        <v>73</v>
       </c>
       <c r="C153">
-        <v>364</v>
+        <v>703</v>
       </c>
       <c r="D153">
-        <v>45</v>
+        <v>511</v>
       </c>
       <c r="E153">
-        <v>8.09</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154">
-        <v>176001003071</v>
+        <v>176001032055</v>
       </c>
       <c r="B154" t="s">
-        <v>162</v>
+        <v>52</v>
       </c>
       <c r="C154">
-        <v>361</v>
+        <v>851</v>
       </c>
       <c r="D154">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E154">
-        <v>5.64</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155">
-        <v>176001003365</v>
+        <v>176001002881</v>
       </c>
       <c r="B155" t="s">
-        <v>163</v>
+        <v>29</v>
       </c>
       <c r="C155">
-        <v>360</v>
+        <v>1185</v>
       </c>
       <c r="D155">
-        <v>20</v>
+        <v>437</v>
       </c>
       <c r="E155">
-        <v>18</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156">
-        <v>276001010994</v>
+        <v>176001028970</v>
       </c>
       <c r="B156" t="s">
-        <v>164</v>
+        <v>19</v>
       </c>
       <c r="C156">
-        <v>358</v>
+        <v>1484</v>
       </c>
       <c r="D156">
-        <v>238</v>
+        <v>89</v>
       </c>
       <c r="E156">
-        <v>1.5</v>
+        <v>16.670000000000002</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157">
-        <v>176001003918</v>
+        <v>176001007166</v>
       </c>
       <c r="B157" t="s">
-        <v>165</v>
+        <v>35</v>
       </c>
       <c r="C157">
-        <v>357</v>
+        <v>1061</v>
       </c>
       <c r="D157">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="E157">
-        <v>17</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158">
-        <v>176001001788</v>
+        <v>176001032063</v>
       </c>
       <c r="B158" t="s">
-        <v>166</v>
+        <v>68</v>
       </c>
       <c r="C158">
-        <v>356</v>
+        <v>752</v>
       </c>
       <c r="D158">
-        <v>284</v>
+        <v>23</v>
       </c>
       <c r="E158">
-        <v>1.25</v>
+        <v>32.700000000000003</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159">
-        <v>176001028040</v>
+        <v>176001007875</v>
       </c>
       <c r="B159" t="s">
-        <v>167</v>
+        <v>46</v>
       </c>
       <c r="C159">
-        <v>351</v>
+        <v>929</v>
       </c>
       <c r="D159">
-        <v>147</v>
+        <v>615</v>
       </c>
       <c r="E159">
-        <v>2.39</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160">
-        <v>176001004442</v>
+        <v>176001030796</v>
       </c>
       <c r="B160" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="C160">
-        <v>346</v>
+        <v>326</v>
       </c>
       <c r="D160">
-        <v>90</v>
+        <v>27</v>
       </c>
       <c r="E160">
-        <v>3.84</v>
+        <v>12.07</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161">
-        <v>176001001826</v>
+        <v>176001001664</v>
       </c>
       <c r="B161" t="s">
-        <v>169</v>
+        <v>54</v>
       </c>
       <c r="C161">
-        <v>345</v>
+        <v>846</v>
       </c>
       <c r="D161">
-        <v>532</v>
+        <v>80</v>
       </c>
       <c r="E161">
-        <v>0.65</v>
+        <v>10.58</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162">
-        <v>176001004744</v>
+        <v>276001005133</v>
       </c>
       <c r="B162" t="s">
-        <v>170</v>
+        <v>225</v>
       </c>
       <c r="C162">
-        <v>343</v>
+        <v>229</v>
       </c>
       <c r="D162">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E162">
-        <v>9.5299999999999994</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163">
-        <v>176001003063</v>
+        <v>176001001800</v>
       </c>
       <c r="B163" t="s">
-        <v>171</v>
+        <v>85</v>
       </c>
       <c r="C163">
-        <v>338</v>
+        <v>609</v>
       </c>
       <c r="D163">
-        <v>15</v>
+        <v>86</v>
       </c>
       <c r="E163">
-        <v>22.53</v>
+        <v>7.08</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164">
-        <v>176001005112</v>
+        <v>176001003225</v>
       </c>
       <c r="B164" t="s">
-        <v>172</v>
+        <v>109</v>
       </c>
       <c r="C164">
-        <v>328</v>
+        <v>486</v>
       </c>
       <c r="D164">
-        <v>102</v>
+        <v>42</v>
       </c>
       <c r="E164">
-        <v>3.22</v>
+        <v>11.57</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165">
-        <v>176001004141</v>
+        <v>176001800214</v>
       </c>
       <c r="B165" t="s">
-        <v>173</v>
+        <v>16</v>
       </c>
       <c r="C165">
-        <v>327</v>
+        <v>1621</v>
       </c>
       <c r="D165">
-        <v>50</v>
+        <v>134</v>
       </c>
       <c r="E165">
-        <v>6.54</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166">
-        <v>176001030796</v>
+        <v>176001022441</v>
       </c>
       <c r="B166" t="s">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="C166">
-        <v>326</v>
+        <v>642</v>
       </c>
       <c r="D166">
-        <v>27</v>
+        <v>80</v>
       </c>
       <c r="E166">
-        <v>12.07</v>
+        <v>8.02</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167">
-        <v>176001028171</v>
+        <v>176001021843</v>
       </c>
       <c r="B167" t="s">
-        <v>175</v>
+        <v>327</v>
       </c>
       <c r="C167">
-        <v>325</v>
+        <v>49</v>
       </c>
       <c r="D167">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="E167">
-        <v>10.83</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168">
-        <v>176001004680</v>
+        <v>176001012488</v>
       </c>
       <c r="B168" t="s">
-        <v>176</v>
+        <v>308</v>
       </c>
       <c r="C168">
-        <v>325</v>
+        <v>105</v>
       </c>
       <c r="D168">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="E168">
-        <v>7.93</v>
+        <v>8.08</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169">
-        <v>176001012216</v>
+        <v>176001008995</v>
       </c>
       <c r="B169" t="s">
-        <v>177</v>
+        <v>294</v>
       </c>
       <c r="C169">
-        <v>322</v>
+        <v>129</v>
       </c>
       <c r="D169">
-        <v>85</v>
+        <v>5</v>
       </c>
       <c r="E169">
-        <v>3.79</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170">
-        <v>276001003394</v>
+        <v>176001001290</v>
       </c>
       <c r="B170" t="s">
-        <v>178</v>
+        <v>312</v>
       </c>
       <c r="C170">
-        <v>320</v>
+        <v>96</v>
       </c>
       <c r="D170">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="E170">
-        <v>14.55</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171">
-        <v>176001004825</v>
+        <v>176001004442</v>
       </c>
       <c r="B171" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="C171">
-        <v>317</v>
+        <v>346</v>
       </c>
       <c r="D171">
-        <v>263</v>
+        <v>90</v>
       </c>
       <c r="E171">
-        <v>1.21</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172">
-        <v>176001005643</v>
+        <v>176001013018</v>
       </c>
       <c r="B172" t="s">
-        <v>180</v>
+        <v>65</v>
       </c>
       <c r="C172">
-        <v>316</v>
+        <v>764</v>
       </c>
       <c r="D172">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E172">
-        <v>31.6</v>
+        <v>25.47</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173">
-        <v>176001004850</v>
+        <v>176001002792</v>
       </c>
       <c r="B173" t="s">
-        <v>181</v>
+        <v>69</v>
       </c>
       <c r="C173">
-        <v>312</v>
+        <v>750</v>
       </c>
       <c r="D173">
-        <v>20</v>
+        <v>498</v>
       </c>
       <c r="E173">
-        <v>15.6</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174">
-        <v>176001003292</v>
+        <v>276001005371</v>
       </c>
       <c r="B174" t="s">
-        <v>182</v>
+        <v>69</v>
       </c>
       <c r="C174">
-        <v>309</v>
+        <v>54</v>
       </c>
       <c r="D174">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E174">
-        <v>9.36</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
@@ -4449,597 +4457,597 @@
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176">
-        <v>176001003373</v>
+        <v>176001006453</v>
       </c>
       <c r="B176" t="s">
-        <v>184</v>
+        <v>255</v>
       </c>
       <c r="C176">
-        <v>306</v>
+        <v>174</v>
       </c>
       <c r="D176">
-        <v>139</v>
+        <v>20</v>
       </c>
       <c r="E176">
-        <v>2.2000000000000002</v>
+        <v>8.6999999999999993</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177">
-        <v>176001006062</v>
+        <v>176001005066</v>
       </c>
       <c r="B177" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C177">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="D177">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E177">
-        <v>10.1</v>
+        <v>14.95</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178">
-        <v>176001004493</v>
+        <v>176001020383</v>
       </c>
       <c r="B178" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="C178">
-        <v>303</v>
+        <v>272</v>
       </c>
       <c r="D178">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E178">
-        <v>4.66</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179">
-        <v>176001005066</v>
+        <v>176001003365</v>
       </c>
       <c r="B179" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="C179">
-        <v>299</v>
+        <v>360</v>
       </c>
       <c r="D179">
         <v>20</v>
       </c>
       <c r="E179">
-        <v>14.95</v>
+        <v>18</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180">
-        <v>276001022232</v>
+        <v>176001002831</v>
       </c>
       <c r="B180" t="s">
-        <v>188</v>
+        <v>286</v>
       </c>
       <c r="C180">
-        <v>298</v>
+        <v>141</v>
       </c>
       <c r="D180">
         <v>30</v>
       </c>
       <c r="E180">
-        <v>9.93</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181">
-        <v>176001004132</v>
+        <v>276001022267</v>
       </c>
       <c r="B181" t="s">
-        <v>189</v>
+        <v>259</v>
       </c>
       <c r="C181">
-        <v>298</v>
+        <v>169</v>
       </c>
       <c r="D181">
-        <v>34</v>
+        <v>220</v>
       </c>
       <c r="E181">
-        <v>8.76</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182">
-        <v>176001005368</v>
+        <v>276001012831</v>
       </c>
       <c r="B182" t="s">
-        <v>190</v>
+        <v>259</v>
       </c>
       <c r="C182">
-        <v>297</v>
+        <v>154</v>
       </c>
       <c r="D182">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E182">
-        <v>14.85</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183">
-        <v>276001005427</v>
+        <v>176001002946</v>
       </c>
       <c r="B183" t="s">
-        <v>191</v>
+        <v>262</v>
       </c>
       <c r="C183">
-        <v>294</v>
+        <v>163</v>
       </c>
       <c r="D183">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="E183">
-        <v>3.5</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184">
-        <v>176001800001</v>
+        <v>176001005406</v>
       </c>
       <c r="B184" t="s">
-        <v>192</v>
+        <v>281</v>
       </c>
       <c r="C184">
-        <v>290</v>
+        <v>148</v>
       </c>
       <c r="D184">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E184">
-        <v>19.329999999999998</v>
+        <v>12.33</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185">
-        <v>176001005031</v>
+        <v>176001004353</v>
       </c>
       <c r="B185" t="s">
-        <v>193</v>
+        <v>295</v>
       </c>
       <c r="C185">
-        <v>290</v>
+        <v>126</v>
       </c>
       <c r="D185">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="E185">
-        <v>7.25</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186">
-        <v>176001003128</v>
+        <v>176001002920</v>
       </c>
       <c r="B186" t="s">
-        <v>194</v>
+        <v>105</v>
       </c>
       <c r="C186">
-        <v>284</v>
+        <v>501</v>
       </c>
       <c r="D186">
-        <v>23</v>
+        <v>135</v>
       </c>
       <c r="E186">
-        <v>12.35</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187">
-        <v>176001002938</v>
+        <v>176001002806</v>
       </c>
       <c r="B187" t="s">
-        <v>195</v>
+        <v>107</v>
       </c>
       <c r="C187">
-        <v>281</v>
+        <v>489</v>
       </c>
       <c r="D187">
-        <v>293</v>
+        <v>455</v>
       </c>
       <c r="E187">
-        <v>0.96</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188">
-        <v>176001030745</v>
+        <v>176001004361</v>
       </c>
       <c r="B188" t="s">
-        <v>196</v>
+        <v>216</v>
       </c>
       <c r="C188">
-        <v>281</v>
+        <v>245</v>
       </c>
       <c r="D188">
         <v>27</v>
       </c>
       <c r="E188">
-        <v>10.41</v>
+        <v>9.07</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189">
-        <v>176001004311</v>
+        <v>276001005532</v>
       </c>
       <c r="B189" t="s">
-        <v>197</v>
+        <v>330</v>
       </c>
       <c r="C189">
-        <v>279</v>
+        <v>40</v>
       </c>
       <c r="D189">
-        <v>96</v>
+        <v>42</v>
       </c>
       <c r="E189">
-        <v>2.91</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190">
-        <v>176001002784</v>
+        <v>276001008434</v>
       </c>
       <c r="B190" t="s">
-        <v>198</v>
+        <v>313</v>
       </c>
       <c r="C190">
-        <v>276</v>
+        <v>95</v>
       </c>
       <c r="D190">
-        <v>96</v>
+        <v>15</v>
       </c>
       <c r="E190">
-        <v>2.88</v>
+        <v>6.33</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191">
-        <v>176001004159</v>
+        <v>176001013026</v>
       </c>
       <c r="B191" t="s">
-        <v>199</v>
+        <v>25</v>
       </c>
       <c r="C191">
-        <v>276</v>
+        <v>1278</v>
       </c>
       <c r="D191">
-        <v>6</v>
+        <v>270</v>
       </c>
       <c r="E191">
-        <v>46</v>
+        <v>4.7300000000000004</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192">
-        <v>176001020383</v>
+        <v>176001003063</v>
       </c>
       <c r="B192" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
       <c r="C192">
-        <v>272</v>
+        <v>338</v>
       </c>
       <c r="D192">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="E192">
-        <v>3.89</v>
+        <v>22.53</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193">
-        <v>176001003942</v>
+        <v>176001006488</v>
       </c>
       <c r="B193" t="s">
-        <v>201</v>
+        <v>277</v>
       </c>
       <c r="C193">
-        <v>268</v>
+        <v>153</v>
       </c>
       <c r="D193">
-        <v>13</v>
+        <v>98</v>
       </c>
       <c r="E193">
-        <v>20.62</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194">
-        <v>176001005309</v>
+        <v>176001023285</v>
       </c>
       <c r="B194" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="C194">
-        <v>266</v>
+        <v>235</v>
       </c>
       <c r="D194">
-        <v>93</v>
+        <v>5</v>
       </c>
       <c r="E194">
-        <v>2.86</v>
+        <v>47</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195">
-        <v>176001003985</v>
+        <v>276001043302</v>
       </c>
       <c r="B195" t="s">
-        <v>203</v>
+        <v>325</v>
       </c>
       <c r="C195">
-        <v>266</v>
+        <v>66</v>
       </c>
       <c r="D195">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E195">
-        <v>10.64</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196">
-        <v>176001042409</v>
+        <v>176001003021</v>
       </c>
       <c r="B196" t="s">
-        <v>204</v>
+        <v>234</v>
       </c>
       <c r="C196">
-        <v>265</v>
+        <v>208</v>
       </c>
       <c r="D196">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="E196">
-        <v>6.62</v>
+        <v>14.86</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197">
-        <v>176001002903</v>
+        <v>176001006062</v>
       </c>
       <c r="B197" t="s">
-        <v>205</v>
+        <v>185</v>
       </c>
       <c r="C197">
-        <v>265</v>
+        <v>303</v>
       </c>
       <c r="D197">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="E197">
-        <v>4.7300000000000004</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198">
-        <v>176001013301</v>
+        <v>276001011745</v>
       </c>
       <c r="B198" t="s">
-        <v>206</v>
+        <v>333</v>
       </c>
       <c r="C198">
-        <v>264</v>
+        <v>31</v>
       </c>
       <c r="D198">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="E198">
-        <v>6.95</v>
+        <v>2.0699999999999998</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199">
-        <v>276001005508</v>
+        <v>276001005494</v>
       </c>
       <c r="B199" t="s">
-        <v>207</v>
+        <v>315</v>
       </c>
       <c r="C199">
-        <v>262</v>
+        <v>91</v>
       </c>
       <c r="D199">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="E199">
-        <v>4.8499999999999996</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200">
-        <v>176001006119</v>
+        <v>176001016009</v>
       </c>
       <c r="B200" t="s">
-        <v>208</v>
+        <v>43</v>
       </c>
       <c r="C200">
-        <v>261</v>
+        <v>965</v>
       </c>
       <c r="D200">
-        <v>297</v>
+        <v>44</v>
       </c>
       <c r="E200">
-        <v>0.88</v>
+        <v>21.93</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201">
-        <v>176001004078</v>
+        <v>176001038070</v>
       </c>
       <c r="B201" t="s">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="C201">
-        <v>258</v>
+        <v>225</v>
       </c>
       <c r="D201">
-        <v>119</v>
+        <v>5</v>
       </c>
       <c r="E201">
-        <v>2.17</v>
+        <v>45</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202">
-        <v>176001040079</v>
+        <v>276001007659</v>
       </c>
       <c r="B202" t="s">
-        <v>210</v>
+        <v>334</v>
       </c>
       <c r="C202">
-        <v>258</v>
+        <v>28</v>
       </c>
       <c r="D202">
-        <v>181</v>
+        <v>10</v>
       </c>
       <c r="E202">
-        <v>1.43</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203">
-        <v>176001004396</v>
+        <v>176001007611</v>
       </c>
       <c r="B203" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="C203">
-        <v>257</v>
+        <v>217</v>
       </c>
       <c r="D203">
-        <v>26</v>
+        <v>99</v>
       </c>
       <c r="E203">
-        <v>9.8800000000000008</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204">
-        <v>176001004965</v>
+        <v>176001004060</v>
       </c>
       <c r="B204" t="s">
-        <v>212</v>
+        <v>123</v>
       </c>
       <c r="C204">
-        <v>256</v>
+        <v>453</v>
       </c>
       <c r="D204">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="E204">
-        <v>17.07</v>
+        <v>16.18</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205">
-        <v>276001006032</v>
+        <v>176001003888</v>
       </c>
       <c r="B205" t="s">
-        <v>213</v>
+        <v>67</v>
       </c>
       <c r="C205">
-        <v>249</v>
+        <v>754</v>
       </c>
       <c r="D205">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="E205">
-        <v>2.33</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206">
-        <v>176001003101</v>
+        <v>176001028040</v>
       </c>
       <c r="B206" t="s">
-        <v>214</v>
+        <v>167</v>
       </c>
       <c r="C206">
-        <v>248</v>
+        <v>351</v>
       </c>
       <c r="D206">
-        <v>10</v>
+        <v>147</v>
       </c>
       <c r="E206">
-        <v>24.8</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207">
-        <v>176001004761</v>
+        <v>176001007093</v>
       </c>
       <c r="B207" t="s">
-        <v>215</v>
+        <v>292</v>
       </c>
       <c r="C207">
-        <v>247</v>
+        <v>131</v>
       </c>
       <c r="D207">
-        <v>145</v>
+        <v>11</v>
       </c>
       <c r="E207">
-        <v>1.7</v>
+        <v>11.91</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208">
-        <v>176001004361</v>
+        <v>176001012089</v>
       </c>
       <c r="B208" t="s">
-        <v>216</v>
+        <v>38</v>
       </c>
       <c r="C208">
-        <v>245</v>
+        <v>1041</v>
       </c>
       <c r="D208">
-        <v>27</v>
+        <v>178</v>
       </c>
       <c r="E208">
-        <v>9.07</v>
+        <v>5.85</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209">
-        <v>176001005091</v>
+        <v>176001003268</v>
       </c>
       <c r="B209" t="s">
-        <v>217</v>
+        <v>303</v>
       </c>
       <c r="C209">
-        <v>244</v>
+        <v>115</v>
       </c>
       <c r="D209">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="E209">
-        <v>3.05</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210">
-        <v>176001002741</v>
+        <v>176001005074</v>
       </c>
       <c r="B210" t="s">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="C210">
-        <v>243</v>
+        <v>624</v>
       </c>
       <c r="D210">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E210">
-        <v>6.94</v>
+        <v>18.91</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
@@ -5061,53 +5069,53 @@
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212">
-        <v>176001043987</v>
+        <v>176001004841</v>
       </c>
       <c r="B212" t="s">
-        <v>142</v>
+        <v>280</v>
       </c>
       <c r="C212">
-        <v>237</v>
+        <v>151</v>
       </c>
       <c r="D212">
-        <v>30</v>
+        <v>136</v>
       </c>
       <c r="E212">
-        <v>7.9</v>
+        <v>1.1100000000000001</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213">
-        <v>176001023285</v>
+        <v>176001005023</v>
       </c>
       <c r="B213" t="s">
-        <v>220</v>
+        <v>94</v>
       </c>
       <c r="C213">
-        <v>235</v>
+        <v>559</v>
       </c>
       <c r="D213">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="E213">
-        <v>47</v>
+        <v>15.97</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214">
-        <v>176001003381</v>
+        <v>176001030699</v>
       </c>
       <c r="B214" t="s">
-        <v>221</v>
+        <v>319</v>
       </c>
       <c r="C214">
-        <v>235</v>
+        <v>71</v>
       </c>
       <c r="D214">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="E214">
-        <v>4.7</v>
+        <v>4.4400000000000004</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
@@ -5129,1325 +5137,1325 @@
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216">
-        <v>176001004663</v>
+        <v>176001004311</v>
       </c>
       <c r="B216" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="C216">
-        <v>230</v>
+        <v>279</v>
       </c>
       <c r="D216">
-        <v>11</v>
+        <v>96</v>
       </c>
       <c r="E216">
-        <v>20.91</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217">
-        <v>176001004949</v>
+        <v>176001003331</v>
       </c>
       <c r="B217" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="C217">
-        <v>230</v>
+        <v>197</v>
       </c>
       <c r="D217">
-        <v>105</v>
+        <v>39</v>
       </c>
       <c r="E217">
-        <v>2.19</v>
+        <v>5.05</v>
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218">
-        <v>276001005133</v>
+        <v>176001004779</v>
       </c>
       <c r="B218" t="s">
-        <v>225</v>
+        <v>266</v>
       </c>
       <c r="C218">
-        <v>229</v>
+        <v>159</v>
       </c>
       <c r="D218">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="E218">
-        <v>5.72</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219">
-        <v>176001008766</v>
+        <v>176001003322</v>
       </c>
       <c r="B219" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="C219">
-        <v>227</v>
+        <v>202</v>
       </c>
       <c r="D219">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="E219">
-        <v>5.68</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220">
-        <v>176001012119</v>
+        <v>176001003381</v>
       </c>
       <c r="B220" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C220">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="D220">
-        <v>103</v>
+        <v>50</v>
       </c>
       <c r="E220">
-        <v>2.1800000000000002</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221">
-        <v>176001038070</v>
+        <v>176001004272</v>
       </c>
       <c r="B221" t="s">
-        <v>228</v>
+        <v>95</v>
       </c>
       <c r="C221">
-        <v>225</v>
+        <v>555</v>
       </c>
       <c r="D221">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="E221">
-        <v>45</v>
+        <v>17.34</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222">
-        <v>176001007611</v>
+        <v>176001005210</v>
       </c>
       <c r="B222" t="s">
-        <v>229</v>
+        <v>287</v>
       </c>
       <c r="C222">
-        <v>217</v>
+        <v>140</v>
       </c>
       <c r="D222">
-        <v>99</v>
+        <v>139</v>
       </c>
       <c r="E222">
-        <v>2.19</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223">
-        <v>176001004264</v>
+        <v>176001012798</v>
       </c>
       <c r="B223" t="s">
-        <v>230</v>
+        <v>96</v>
       </c>
       <c r="C223">
-        <v>212</v>
+        <v>549</v>
       </c>
       <c r="D223">
-        <v>113</v>
+        <v>283</v>
       </c>
       <c r="E223">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224">
-        <v>176001001001</v>
+        <v>176001004426</v>
       </c>
       <c r="B224" t="s">
-        <v>231</v>
+        <v>270</v>
       </c>
       <c r="C224">
-        <v>210</v>
+        <v>156</v>
       </c>
       <c r="D224">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E224">
-        <v>10.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225">
-        <v>276001005231</v>
+        <v>176001003012</v>
       </c>
       <c r="B225" t="s">
-        <v>232</v>
+        <v>113</v>
       </c>
       <c r="C225">
-        <v>209</v>
+        <v>477</v>
       </c>
       <c r="D225">
-        <v>29</v>
+        <v>372</v>
       </c>
       <c r="E225">
-        <v>7.21</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226">
-        <v>176001001656</v>
+        <v>176001004281</v>
       </c>
       <c r="B226" t="s">
-        <v>233</v>
+        <v>158</v>
       </c>
       <c r="C226">
-        <v>208</v>
+        <v>369</v>
       </c>
       <c r="D226">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="E226">
-        <v>3.25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227">
-        <v>176001003021</v>
+        <v>176001005261</v>
       </c>
       <c r="B227" t="s">
-        <v>234</v>
+        <v>263</v>
       </c>
       <c r="C227">
-        <v>208</v>
+        <v>161</v>
       </c>
       <c r="D227">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="E227">
-        <v>14.86</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228">
-        <v>176001004124</v>
+        <v>176001001788</v>
       </c>
       <c r="B228" t="s">
-        <v>235</v>
+        <v>166</v>
       </c>
       <c r="C228">
-        <v>204</v>
+        <v>356</v>
       </c>
       <c r="D228">
-        <v>25</v>
+        <v>284</v>
       </c>
       <c r="E228">
-        <v>8.16</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229">
-        <v>176001004213</v>
+        <v>176001008421</v>
       </c>
       <c r="B229" t="s">
-        <v>236</v>
+        <v>283</v>
       </c>
       <c r="C229">
-        <v>202</v>
+        <v>144</v>
       </c>
       <c r="D229">
-        <v>51</v>
+        <v>110</v>
       </c>
       <c r="E229">
-        <v>3.96</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230">
-        <v>176001003322</v>
+        <v>376001017608</v>
       </c>
       <c r="B230" t="s">
-        <v>237</v>
+        <v>62</v>
       </c>
       <c r="C230">
-        <v>202</v>
+        <v>797</v>
       </c>
       <c r="D230">
-        <v>31</v>
+        <v>139</v>
       </c>
       <c r="E230">
-        <v>6.52</v>
+        <v>5.73</v>
       </c>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231">
-        <v>176001003331</v>
+        <v>176001003411</v>
       </c>
       <c r="B231" t="s">
-        <v>238</v>
+        <v>81</v>
       </c>
       <c r="C231">
-        <v>197</v>
+        <v>628</v>
       </c>
       <c r="D231">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="E231">
-        <v>5.05</v>
+        <v>28.55</v>
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232">
-        <v>176001002822</v>
+        <v>176001004574</v>
       </c>
       <c r="B232" t="s">
-        <v>239</v>
+        <v>274</v>
       </c>
       <c r="C232">
-        <v>195</v>
+        <v>154</v>
       </c>
       <c r="D232">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E232">
-        <v>19.5</v>
+        <v>8.11</v>
       </c>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233">
-        <v>176001002814</v>
+        <v>176001030478</v>
       </c>
       <c r="B233" t="s">
-        <v>240</v>
+        <v>80</v>
       </c>
       <c r="C233">
-        <v>195</v>
+        <v>632</v>
       </c>
       <c r="D233">
-        <v>96</v>
+        <v>431</v>
       </c>
       <c r="E233">
-        <v>2.0299999999999998</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234">
-        <v>176001008791</v>
+        <v>176001005643</v>
       </c>
       <c r="B234" t="s">
-        <v>241</v>
+        <v>180</v>
       </c>
       <c r="C234">
-        <v>195</v>
+        <v>316</v>
       </c>
       <c r="D234">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="E234">
-        <v>8.1199999999999992</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235">
-        <v>176001042778</v>
+        <v>176001004213</v>
       </c>
       <c r="B235" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="C235">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="D235">
-        <v>116</v>
+        <v>51</v>
       </c>
       <c r="E235">
-        <v>1.65</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236">
-        <v>176001003209</v>
+        <v>176001002750</v>
       </c>
       <c r="B236" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="C236">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="D236">
-        <v>184</v>
+        <v>36</v>
       </c>
       <c r="E236">
-        <v>1.02</v>
+        <v>4.8899999999999997</v>
       </c>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237">
-        <v>176001004876</v>
+        <v>176001004680</v>
       </c>
       <c r="B237" t="s">
-        <v>244</v>
+        <v>176</v>
       </c>
       <c r="C237">
-        <v>184</v>
+        <v>325</v>
       </c>
       <c r="D237">
-        <v>309</v>
+        <v>41</v>
       </c>
       <c r="E237">
-        <v>0.6</v>
+        <v>7.93</v>
       </c>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238">
-        <v>176001004019</v>
+        <v>276001011753</v>
       </c>
       <c r="B238" t="s">
-        <v>245</v>
+        <v>340</v>
       </c>
       <c r="C238">
-        <v>184</v>
+        <v>7</v>
       </c>
       <c r="D238">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="E238">
-        <v>2.63</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239">
-        <v>176001007298</v>
+        <v>176001800419</v>
       </c>
       <c r="B239" t="s">
-        <v>246</v>
+        <v>126</v>
       </c>
       <c r="C239">
-        <v>184</v>
+        <v>446</v>
       </c>
       <c r="D239">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="E239">
-        <v>3.47</v>
+        <v>10.62</v>
       </c>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240">
-        <v>176001009011</v>
+        <v>176001003209</v>
       </c>
       <c r="B240" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C240">
+        <v>188</v>
+      </c>
+      <c r="D240">
         <v>184</v>
       </c>
-      <c r="D240">
-        <v>31</v>
-      </c>
       <c r="E240">
-        <v>5.94</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241">
-        <v>176001004469</v>
+        <v>376001023667</v>
       </c>
       <c r="B241" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="C241">
-        <v>183</v>
+        <v>154</v>
       </c>
       <c r="D241">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="E241">
-        <v>7.04</v>
+        <v>12.83</v>
       </c>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242">
-        <v>176001002733</v>
+        <v>176001004248</v>
       </c>
       <c r="B242" t="s">
-        <v>249</v>
+        <v>135</v>
       </c>
       <c r="C242">
-        <v>180</v>
+        <v>409</v>
       </c>
       <c r="D242">
-        <v>15</v>
+        <v>111</v>
       </c>
       <c r="E242">
-        <v>12</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243">
-        <v>276001011184</v>
+        <v>176001003837</v>
       </c>
       <c r="B243" t="s">
-        <v>250</v>
+        <v>128</v>
       </c>
       <c r="C243">
-        <v>179</v>
+        <v>438</v>
       </c>
       <c r="D243">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="E243">
-        <v>11.19</v>
+        <v>12.51</v>
       </c>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244">
-        <v>176001004116</v>
+        <v>176001004761</v>
       </c>
       <c r="B244" t="s">
-        <v>251</v>
+        <v>215</v>
       </c>
       <c r="C244">
-        <v>177</v>
+        <v>247</v>
       </c>
       <c r="D244">
-        <v>13</v>
+        <v>145</v>
       </c>
       <c r="E244">
-        <v>13.62</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245">
-        <v>176001004035</v>
+        <v>276001004897</v>
       </c>
       <c r="B245" t="s">
-        <v>252</v>
+        <v>326</v>
       </c>
       <c r="C245">
-        <v>176</v>
+        <v>60</v>
       </c>
       <c r="D245">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="E245">
-        <v>7.65</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246">
-        <v>176001002750</v>
+        <v>176001006496</v>
       </c>
       <c r="B246" t="s">
-        <v>253</v>
+        <v>154</v>
       </c>
       <c r="C246">
-        <v>176</v>
+        <v>380</v>
       </c>
       <c r="D246">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="E246">
-        <v>4.8899999999999997</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A247">
-        <v>376001020501</v>
+        <v>176001004515</v>
       </c>
       <c r="B247" t="s">
-        <v>254</v>
+        <v>22</v>
       </c>
       <c r="C247">
-        <v>174</v>
+        <v>1344</v>
       </c>
       <c r="D247">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E247">
-        <v>17.399999999999999</v>
+        <v>112</v>
       </c>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A248">
-        <v>176001006453</v>
+        <v>176001004159</v>
       </c>
       <c r="B248" t="s">
-        <v>255</v>
+        <v>199</v>
       </c>
       <c r="C248">
-        <v>174</v>
+        <v>276</v>
       </c>
       <c r="D248">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E248">
-        <v>8.6999999999999993</v>
+        <v>46</v>
       </c>
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249">
-        <v>176001014120</v>
+        <v>176001006445</v>
       </c>
       <c r="B249" t="s">
-        <v>256</v>
+        <v>78</v>
       </c>
       <c r="C249">
-        <v>170</v>
+        <v>689</v>
       </c>
       <c r="D249">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="E249">
-        <v>8.5</v>
+        <v>15.66</v>
       </c>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250">
-        <v>176001021461</v>
+        <v>176001800401</v>
       </c>
       <c r="B250" t="s">
-        <v>257</v>
+        <v>28</v>
       </c>
       <c r="C250">
-        <v>170</v>
+        <v>1213</v>
       </c>
       <c r="D250">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E250">
-        <v>8.5</v>
+        <v>40.43</v>
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A251">
-        <v>176001004451</v>
+        <v>176001030117</v>
       </c>
       <c r="B251" t="s">
-        <v>258</v>
+        <v>74</v>
       </c>
       <c r="C251">
-        <v>170</v>
+        <v>703</v>
       </c>
       <c r="D251">
-        <v>149</v>
+        <v>275</v>
       </c>
       <c r="E251">
-        <v>1.1399999999999999</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A252">
-        <v>276001022267</v>
+        <v>176001042280</v>
       </c>
       <c r="B252" t="s">
-        <v>259</v>
+        <v>124</v>
       </c>
       <c r="C252">
-        <v>169</v>
+        <v>452</v>
       </c>
       <c r="D252">
-        <v>220</v>
+        <v>102</v>
       </c>
       <c r="E252">
-        <v>0.77</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253">
-        <v>276001800481</v>
+        <v>176001004345</v>
       </c>
       <c r="B253" t="s">
-        <v>260</v>
+        <v>317</v>
       </c>
       <c r="C253">
-        <v>166</v>
+        <v>74</v>
       </c>
       <c r="D253">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E253">
-        <v>5.53</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254">
-        <v>276001011770</v>
+        <v>176001007336</v>
       </c>
       <c r="B254" t="s">
-        <v>261</v>
+        <v>156</v>
       </c>
       <c r="C254">
-        <v>164</v>
+        <v>372</v>
       </c>
       <c r="D254">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="E254">
-        <v>8.1999999999999993</v>
+        <v>10.33</v>
       </c>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255">
-        <v>176001002946</v>
+        <v>176001006470</v>
       </c>
       <c r="B255" t="s">
-        <v>262</v>
+        <v>129</v>
       </c>
       <c r="C255">
-        <v>163</v>
+        <v>433</v>
       </c>
       <c r="D255">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="E255">
-        <v>2.72</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256">
-        <v>176001005261</v>
+        <v>176001002741</v>
       </c>
       <c r="B256" t="s">
-        <v>263</v>
+        <v>218</v>
       </c>
       <c r="C256">
-        <v>161</v>
+        <v>243</v>
       </c>
       <c r="D256">
-        <v>94</v>
+        <v>35</v>
       </c>
       <c r="E256">
-        <v>1.71</v>
+        <v>6.94</v>
       </c>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257">
-        <v>176001004612</v>
+        <v>176001004141</v>
       </c>
       <c r="B257" t="s">
-        <v>264</v>
+        <v>173</v>
       </c>
       <c r="C257">
-        <v>160</v>
+        <v>327</v>
       </c>
       <c r="D257">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="E257">
-        <v>1.68</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A258">
-        <v>176001800249</v>
+        <v>176001022416</v>
       </c>
       <c r="B258" t="s">
-        <v>265</v>
+        <v>51</v>
       </c>
       <c r="C258">
-        <v>160</v>
+        <v>859</v>
       </c>
       <c r="D258">
-        <v>46</v>
+        <v>214</v>
       </c>
       <c r="E258">
-        <v>3.48</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A259">
-        <v>176001004779</v>
+        <v>176001004655</v>
       </c>
       <c r="B259" t="s">
-        <v>266</v>
+        <v>114</v>
       </c>
       <c r="C259">
-        <v>159</v>
+        <v>476</v>
       </c>
       <c r="D259">
-        <v>147</v>
+        <v>40</v>
       </c>
       <c r="E259">
-        <v>1.08</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A260">
-        <v>176001004710</v>
+        <v>176001003985</v>
       </c>
       <c r="B260" t="s">
-        <v>267</v>
+        <v>203</v>
       </c>
       <c r="C260">
-        <v>159</v>
+        <v>266</v>
       </c>
       <c r="D260">
-        <v>113</v>
+        <v>25</v>
       </c>
       <c r="E260">
-        <v>1.41</v>
+        <v>10.64</v>
       </c>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A261">
-        <v>176001003896</v>
+        <v>176001005015</v>
       </c>
       <c r="B261" t="s">
-        <v>268</v>
+        <v>88</v>
       </c>
       <c r="C261">
-        <v>157</v>
+        <v>591</v>
       </c>
       <c r="D261">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="E261">
-        <v>11.21</v>
+        <v>12.57</v>
       </c>
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A262">
-        <v>176001003098</v>
+        <v>276001005451</v>
       </c>
       <c r="B262" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="C262">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="D262">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E262">
-        <v>7.14</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A263">
-        <v>176001004426</v>
+        <v>176001002784</v>
       </c>
       <c r="B263" t="s">
-        <v>270</v>
+        <v>198</v>
       </c>
       <c r="C263">
-        <v>156</v>
+        <v>276</v>
       </c>
       <c r="D263">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="E263">
-        <v>6.5</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A264">
-        <v>176001800036</v>
+        <v>176001004493</v>
       </c>
       <c r="B264" t="s">
-        <v>271</v>
+        <v>186</v>
       </c>
       <c r="C264">
-        <v>156</v>
+        <v>303</v>
       </c>
       <c r="D264">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="E264">
-        <v>9.75</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A265">
-        <v>276001005141</v>
+        <v>276001005231</v>
       </c>
       <c r="B265" t="s">
-        <v>272</v>
+        <v>232</v>
       </c>
       <c r="C265">
-        <v>156</v>
+        <v>209</v>
       </c>
       <c r="D265">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="E265">
-        <v>3.47</v>
+        <v>7.21</v>
       </c>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A266">
-        <v>176001012763</v>
+        <v>176001004965</v>
       </c>
       <c r="B266" t="s">
-        <v>273</v>
+        <v>212</v>
       </c>
       <c r="C266">
-        <v>155</v>
+        <v>256</v>
       </c>
       <c r="D266">
-        <v>97</v>
+        <v>15</v>
       </c>
       <c r="E266">
-        <v>1.6</v>
+        <v>17.07</v>
       </c>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A267">
-        <v>276001012831</v>
+        <v>176001004949</v>
       </c>
       <c r="B267" t="s">
-        <v>259</v>
+        <v>224</v>
       </c>
       <c r="C267">
-        <v>154</v>
+        <v>230</v>
       </c>
       <c r="D267">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="E267">
-        <v>3.08</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A268">
-        <v>176001004574</v>
+        <v>176001003071</v>
       </c>
       <c r="B268" t="s">
-        <v>274</v>
+        <v>162</v>
       </c>
       <c r="C268">
-        <v>154</v>
+        <v>361</v>
       </c>
       <c r="D268">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="E268">
-        <v>8.11</v>
+        <v>5.64</v>
       </c>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A269">
-        <v>176001004591</v>
+        <v>176001012976</v>
       </c>
       <c r="B269" t="s">
-        <v>275</v>
+        <v>61</v>
       </c>
       <c r="C269">
-        <v>154</v>
+        <v>800</v>
       </c>
       <c r="D269">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="E269">
-        <v>5.92</v>
+        <v>16</v>
       </c>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A270">
-        <v>376001023667</v>
+        <v>176001005082</v>
       </c>
       <c r="B270" t="s">
-        <v>276</v>
+        <v>91</v>
       </c>
       <c r="C270">
-        <v>154</v>
+        <v>570</v>
       </c>
       <c r="D270">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="E270">
-        <v>12.83</v>
+        <v>14.25</v>
       </c>
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A271">
-        <v>176001006488</v>
+        <v>176001003101</v>
       </c>
       <c r="B271" t="s">
-        <v>277</v>
+        <v>214</v>
       </c>
       <c r="C271">
-        <v>153</v>
+        <v>248</v>
       </c>
       <c r="D271">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="E271">
-        <v>1.56</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A272">
-        <v>176001004043</v>
+        <v>176001004523</v>
       </c>
       <c r="B272" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="C272">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="D272">
-        <v>6</v>
+        <v>206</v>
       </c>
       <c r="E272">
-        <v>25.33</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A273">
-        <v>176001002873</v>
+        <v>176001015860</v>
       </c>
       <c r="B273" t="s">
-        <v>279</v>
+        <v>329</v>
       </c>
       <c r="C273">
-        <v>151</v>
+        <v>42</v>
       </c>
       <c r="D273">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E273">
-        <v>10.07</v>
+        <v>21</v>
       </c>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A274">
-        <v>176001004841</v>
+        <v>276001004838</v>
       </c>
       <c r="B274" t="s">
-        <v>280</v>
+        <v>328</v>
       </c>
       <c r="C274">
-        <v>151</v>
+        <v>49</v>
       </c>
       <c r="D274">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="E274">
-        <v>1.1100000000000001</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A275">
-        <v>176001003039</v>
+        <v>276001800260</v>
       </c>
       <c r="B275" t="s">
-        <v>170</v>
+        <v>132</v>
       </c>
       <c r="C275">
-        <v>148</v>
+        <v>419</v>
       </c>
       <c r="D275">
-        <v>4</v>
+        <v>74</v>
       </c>
       <c r="E275">
-        <v>37</v>
+        <v>5.66</v>
       </c>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A276">
-        <v>176001005406</v>
+        <v>176001015941</v>
       </c>
       <c r="B276" t="s">
-        <v>281</v>
+        <v>150</v>
       </c>
       <c r="C276">
-        <v>148</v>
+        <v>385</v>
       </c>
       <c r="D276">
-        <v>12</v>
+        <v>107</v>
       </c>
       <c r="E276">
-        <v>12.33</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A277">
-        <v>476001020719</v>
+        <v>176001003098</v>
       </c>
       <c r="B277" t="s">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="C277">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="D277">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E277">
-        <v>5.48</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A278">
-        <v>176001008421</v>
+        <v>176001006461</v>
       </c>
       <c r="B278" t="s">
-        <v>283</v>
+        <v>99</v>
       </c>
       <c r="C278">
-        <v>144</v>
+        <v>536</v>
       </c>
       <c r="D278">
-        <v>110</v>
+        <v>222</v>
       </c>
       <c r="E278">
-        <v>1.31</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A279">
-        <v>276001005451</v>
+        <v>176001004094</v>
       </c>
       <c r="B279" t="s">
-        <v>284</v>
+        <v>131</v>
       </c>
       <c r="C279">
-        <v>142</v>
+        <v>421</v>
       </c>
       <c r="D279">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E279">
-        <v>14.2</v>
+        <v>23.39</v>
       </c>
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A280">
-        <v>176001004191</v>
+        <v>176001012763</v>
       </c>
       <c r="B280" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="C280">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="D280">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E280">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A281">
-        <v>176001002831</v>
+        <v>176001005112</v>
       </c>
       <c r="B281" t="s">
-        <v>286</v>
+        <v>172</v>
       </c>
       <c r="C281">
-        <v>141</v>
+        <v>328</v>
       </c>
       <c r="D281">
-        <v>30</v>
+        <v>102</v>
       </c>
       <c r="E281">
-        <v>4.7</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A282">
-        <v>176001005210</v>
+        <v>176001012119</v>
       </c>
       <c r="B282" t="s">
-        <v>287</v>
+        <v>227</v>
       </c>
       <c r="C282">
-        <v>140</v>
+        <v>225</v>
       </c>
       <c r="D282">
-        <v>139</v>
+        <v>103</v>
       </c>
       <c r="E282">
-        <v>1.01</v>
+        <v>2.1800000000000002</v>
       </c>
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A283">
-        <v>276001008574</v>
+        <v>176001004612</v>
       </c>
       <c r="B283" t="s">
-        <v>288</v>
+        <v>264</v>
       </c>
       <c r="C283">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="D283">
-        <v>28</v>
+        <v>95</v>
       </c>
       <c r="E283">
-        <v>4.82</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A284">
-        <v>176001004523</v>
+        <v>276001005877</v>
       </c>
       <c r="B284" t="s">
-        <v>289</v>
+        <v>143</v>
       </c>
       <c r="C284">
-        <v>134</v>
+        <v>392</v>
       </c>
       <c r="D284">
-        <v>206</v>
+        <v>137</v>
       </c>
       <c r="E284">
-        <v>0.65</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A285">
-        <v>176001004582</v>
+        <v>176001004825</v>
       </c>
       <c r="B285" t="s">
-        <v>290</v>
+        <v>179</v>
       </c>
       <c r="C285">
-        <v>133</v>
+        <v>317</v>
       </c>
       <c r="D285">
-        <v>49</v>
+        <v>263</v>
       </c>
       <c r="E285">
-        <v>2.71</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A286">
-        <v>176001042786</v>
+        <v>176001004035</v>
       </c>
       <c r="B286" t="s">
-        <v>291</v>
+        <v>252</v>
       </c>
       <c r="C286">
-        <v>131</v>
+        <v>176</v>
       </c>
       <c r="D286">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="E286">
-        <v>3.2</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A287">
-        <v>176001007093</v>
+        <v>176001004744</v>
       </c>
       <c r="B287" t="s">
-        <v>292</v>
+        <v>170</v>
       </c>
       <c r="C287">
-        <v>131</v>
+        <v>343</v>
       </c>
       <c r="D287">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="E287">
-        <v>11.91</v>
+        <v>9.5299999999999994</v>
       </c>
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A288">
-        <v>276001007641</v>
+        <v>176001003039</v>
       </c>
       <c r="B288" t="s">
-        <v>293</v>
+        <v>170</v>
       </c>
       <c r="C288">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="D288">
-        <v>83</v>
+        <v>4</v>
       </c>
       <c r="E288">
-        <v>1.57</v>
+        <v>37</v>
       </c>
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A289">
-        <v>176001008995</v>
+        <v>176001004132</v>
       </c>
       <c r="B289" t="s">
-        <v>294</v>
+        <v>189</v>
       </c>
       <c r="C289">
-        <v>129</v>
+        <v>298</v>
       </c>
       <c r="D289">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="E289">
-        <v>25.8</v>
+        <v>8.76</v>
       </c>
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A290">
-        <v>176001004353</v>
+        <v>176001005414</v>
       </c>
       <c r="B290" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="C290">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="D290">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E290">
-        <v>8.4</v>
+        <v>16.43</v>
       </c>
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A291">
-        <v>276001005460</v>
+        <v>176001003055</v>
       </c>
       <c r="B291" t="s">
-        <v>296</v>
+        <v>75</v>
       </c>
       <c r="C291">
-        <v>125</v>
+        <v>694</v>
       </c>
       <c r="D291">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="E291">
-        <v>1.6</v>
+        <v>7.23</v>
       </c>
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A292">
-        <v>176001007891</v>
+        <v>376001017438</v>
       </c>
       <c r="B292" t="s">
-        <v>297</v>
+        <v>82</v>
       </c>
       <c r="C292">
-        <v>123</v>
+        <v>625</v>
       </c>
       <c r="D292">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="E292">
-        <v>7.69</v>
+        <v>15.62</v>
       </c>
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A293">
-        <v>176001012844</v>
+        <v>276001011770</v>
       </c>
       <c r="B293" t="s">
-        <v>298</v>
+        <v>261</v>
       </c>
       <c r="C293">
-        <v>123</v>
+        <v>164</v>
       </c>
       <c r="D293">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E293">
         <v>8.1999999999999993</v>
@@ -6455,770 +6463,775 @@
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A294">
-        <v>176001007638</v>
+        <v>176001005309</v>
       </c>
       <c r="B294" t="s">
-        <v>299</v>
+        <v>202</v>
       </c>
       <c r="C294">
-        <v>122</v>
+        <v>266</v>
       </c>
       <c r="D294">
-        <v>119</v>
+        <v>93</v>
       </c>
       <c r="E294">
-        <v>1.03</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A295">
-        <v>176001004973</v>
+        <v>176001042786</v>
       </c>
       <c r="B295" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="C295">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="D295">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="E295">
-        <v>6.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A296">
-        <v>176001005431</v>
+        <v>176001004230</v>
       </c>
       <c r="B296" t="s">
-        <v>301</v>
+        <v>122</v>
       </c>
       <c r="C296">
-        <v>119</v>
+        <v>455</v>
       </c>
       <c r="D296">
-        <v>25</v>
+        <v>254</v>
       </c>
       <c r="E296">
-        <v>4.76</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A297">
-        <v>176001003934</v>
+        <v>276001005427</v>
       </c>
       <c r="B297" t="s">
-        <v>302</v>
+        <v>191</v>
       </c>
       <c r="C297">
-        <v>119</v>
+        <v>294</v>
       </c>
       <c r="D297">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="E297">
-        <v>1.0900000000000001</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A298">
-        <v>176001003268</v>
+        <v>176001021461</v>
       </c>
       <c r="B298" t="s">
-        <v>303</v>
+        <v>257</v>
       </c>
       <c r="C298">
-        <v>115</v>
+        <v>170</v>
       </c>
       <c r="D298">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="E298">
-        <v>1.8</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A299">
-        <v>176001005414</v>
+        <v>176001003292</v>
       </c>
       <c r="B299" t="s">
-        <v>304</v>
+        <v>182</v>
       </c>
       <c r="C299">
-        <v>115</v>
+        <v>309</v>
       </c>
       <c r="D299">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="E299">
-        <v>16.43</v>
+        <v>9.36</v>
       </c>
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A300">
-        <v>176001003861</v>
+        <v>176001013271</v>
       </c>
       <c r="B300" t="s">
-        <v>305</v>
+        <v>331</v>
       </c>
       <c r="C300">
-        <v>115</v>
+        <v>36</v>
       </c>
       <c r="D300">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E300">
-        <v>3.83</v>
+        <v>2</v>
       </c>
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A301">
-        <v>176001004698</v>
+        <v>176001800001</v>
       </c>
       <c r="B301" t="s">
-        <v>306</v>
+        <v>192</v>
       </c>
       <c r="C301">
-        <v>112</v>
+        <v>290</v>
       </c>
       <c r="D301">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E301">
-        <v>12.44</v>
+        <v>19.329999999999998</v>
       </c>
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A302">
-        <v>176001003870</v>
+        <v>176001015959</v>
       </c>
       <c r="B302" t="s">
-        <v>307</v>
+        <v>26</v>
       </c>
       <c r="C302">
-        <v>107</v>
+        <v>1245</v>
       </c>
       <c r="D302">
-        <v>14</v>
+        <v>293</v>
       </c>
       <c r="E302">
-        <v>7.64</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A303">
-        <v>176001012488</v>
+        <v>176001004582</v>
       </c>
       <c r="B303" t="s">
-        <v>308</v>
+        <v>290</v>
       </c>
       <c r="C303">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="D303">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="E303">
-        <v>8.08</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A304">
-        <v>276001005443</v>
+        <v>176001003403</v>
       </c>
       <c r="B304" t="s">
-        <v>309</v>
+        <v>86</v>
       </c>
       <c r="C304">
-        <v>104</v>
+        <v>597</v>
       </c>
       <c r="D304">
-        <v>32</v>
+        <v>94</v>
       </c>
       <c r="E304">
-        <v>3.25</v>
+        <v>6.35</v>
       </c>
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A305">
-        <v>176001008677</v>
+        <v>276001005541</v>
       </c>
       <c r="B305" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="C305">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="D305">
-        <v>11</v>
+        <v>88</v>
       </c>
       <c r="E305">
-        <v>9.18</v>
+        <v>0.81</v>
       </c>
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A306">
-        <v>176001005058</v>
+        <v>176001007298</v>
       </c>
       <c r="B306" t="s">
-        <v>311</v>
+        <v>246</v>
       </c>
       <c r="C306">
-        <v>100</v>
+        <v>184</v>
       </c>
       <c r="D306">
-        <v>111</v>
+        <v>53</v>
       </c>
       <c r="E306">
-        <v>0.9</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A307">
-        <v>176001001290</v>
+        <v>176001015983</v>
       </c>
       <c r="B307" t="s">
-        <v>312</v>
+        <v>21</v>
       </c>
       <c r="C307">
-        <v>96</v>
+        <v>1430</v>
       </c>
       <c r="D307">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="E307">
-        <v>3.1</v>
+        <v>24.66</v>
       </c>
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A308">
-        <v>276001008434</v>
+        <v>276001003238</v>
       </c>
       <c r="B308" t="s">
-        <v>313</v>
+        <v>332</v>
       </c>
       <c r="C308">
-        <v>95</v>
+        <v>33</v>
       </c>
       <c r="D308">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E308">
-        <v>6.33</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A309">
-        <v>176001800231</v>
+        <v>176001004990</v>
       </c>
       <c r="B309" t="s">
-        <v>314</v>
+        <v>89</v>
       </c>
       <c r="C309">
-        <v>94</v>
+        <v>585</v>
       </c>
       <c r="D309">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="E309">
-        <v>1.31</v>
+        <v>16.25</v>
       </c>
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A310">
-        <v>276001005494</v>
+        <v>176001001001</v>
       </c>
       <c r="B310" t="s">
-        <v>315</v>
+        <v>231</v>
       </c>
       <c r="C310">
-        <v>91</v>
+        <v>210</v>
       </c>
       <c r="D310">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E310">
-        <v>3.25</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A311">
-        <v>176001005333</v>
+        <v>176001004558</v>
       </c>
       <c r="B311" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="C311">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="D311">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="E311">
-        <v>1.58</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A312">
-        <v>176001004345</v>
+        <v>176001004914</v>
       </c>
       <c r="B312" t="s">
-        <v>317</v>
+        <v>108</v>
       </c>
       <c r="C312">
-        <v>74</v>
+        <v>488</v>
       </c>
       <c r="D312">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E312">
-        <v>2.96</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A313">
-        <v>276001005541</v>
+        <v>176001007905</v>
       </c>
       <c r="B313" t="s">
-        <v>318</v>
+        <v>133</v>
       </c>
       <c r="C313">
-        <v>71</v>
+        <v>415</v>
       </c>
       <c r="D313">
-        <v>88</v>
+        <v>31</v>
       </c>
       <c r="E313">
-        <v>0.81</v>
+        <v>13.39</v>
       </c>
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A314">
-        <v>176001030699</v>
+        <v>176001002903</v>
       </c>
       <c r="B314" t="s">
-        <v>319</v>
+        <v>205</v>
       </c>
       <c r="C314">
-        <v>71</v>
+        <v>265</v>
       </c>
       <c r="D314">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="E314">
-        <v>4.4400000000000004</v>
+        <v>4.7300000000000004</v>
       </c>
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A315">
-        <v>176001004558</v>
+        <v>276001006032</v>
       </c>
       <c r="B315" t="s">
-        <v>320</v>
+        <v>213</v>
       </c>
       <c r="C315">
-        <v>70</v>
+        <v>249</v>
       </c>
       <c r="D315">
-        <v>27</v>
+        <v>107</v>
       </c>
       <c r="E315">
-        <v>2.59</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A316">
-        <v>276001005559</v>
+        <v>176001042778</v>
       </c>
       <c r="B316" t="s">
-        <v>321</v>
+        <v>242</v>
       </c>
       <c r="C316">
-        <v>69</v>
+        <v>191</v>
       </c>
       <c r="D316">
-        <v>83</v>
+        <v>116</v>
       </c>
       <c r="E316">
-        <v>0.83</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A317">
-        <v>176001003004</v>
+        <v>176001004671</v>
       </c>
       <c r="B317" t="s">
-        <v>322</v>
+        <v>145</v>
       </c>
       <c r="C317">
-        <v>68</v>
+        <v>391</v>
       </c>
       <c r="D317">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E317">
-        <v>13.6</v>
+        <v>24.44</v>
       </c>
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A318">
-        <v>276001042756</v>
+        <v>176001009045</v>
       </c>
       <c r="B318" t="s">
-        <v>323</v>
+        <v>71</v>
       </c>
       <c r="C318">
-        <v>68</v>
+        <v>730</v>
       </c>
       <c r="D318">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="E318">
-        <v>0.84</v>
+        <v>18.25</v>
       </c>
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A319">
-        <v>276001005150</v>
+        <v>176001030745</v>
       </c>
       <c r="B319" t="s">
-        <v>324</v>
+        <v>196</v>
       </c>
       <c r="C319">
-        <v>67</v>
+        <v>281</v>
       </c>
       <c r="D319">
-        <v>107</v>
+        <v>27</v>
       </c>
       <c r="E319">
-        <v>0.63</v>
+        <v>10.41</v>
       </c>
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A320">
-        <v>276001043302</v>
+        <v>176001005431</v>
       </c>
       <c r="B320" t="s">
-        <v>325</v>
+        <v>301</v>
       </c>
       <c r="C320">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D320">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E320">
-        <v>2.44</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A321">
-        <v>276001004897</v>
+        <v>276001005559</v>
       </c>
       <c r="B321" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="C321">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="D321">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="E321">
-        <v>1.05</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A322">
-        <v>276001005371</v>
+        <v>276001025452</v>
       </c>
       <c r="B322" t="s">
-        <v>69</v>
+        <v>120</v>
       </c>
       <c r="C322">
-        <v>54</v>
+        <v>457</v>
       </c>
       <c r="D322">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E322">
-        <v>3</v>
+        <v>15.23</v>
       </c>
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A323">
-        <v>176001021843</v>
+        <v>176001004698</v>
       </c>
       <c r="B323" t="s">
-        <v>327</v>
+        <v>306</v>
       </c>
       <c r="C323">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="D323">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E323">
-        <v>24.5</v>
+        <v>12.44</v>
       </c>
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A324">
-        <v>276001004838</v>
+        <v>176001004396</v>
       </c>
       <c r="B324" t="s">
-        <v>328</v>
+        <v>211</v>
       </c>
       <c r="C324">
-        <v>49</v>
+        <v>257</v>
       </c>
       <c r="D324">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="E324">
-        <v>0.63</v>
+        <v>9.8800000000000008</v>
       </c>
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A325">
-        <v>176001015860</v>
+        <v>276001005443</v>
       </c>
       <c r="B325" t="s">
-        <v>329</v>
+        <v>309</v>
       </c>
       <c r="C325">
-        <v>42</v>
+        <v>104</v>
       </c>
       <c r="D325">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="E325">
-        <v>21</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A326">
-        <v>276001005532</v>
+        <v>276001020434</v>
       </c>
       <c r="B326" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="C326">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="D326">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="E326">
-        <v>0.95</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A327">
-        <v>176001013271</v>
+        <v>176001800061</v>
       </c>
       <c r="B327" t="s">
-        <v>331</v>
+        <v>130</v>
       </c>
       <c r="C327">
-        <v>36</v>
+        <v>424</v>
       </c>
       <c r="D327">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E327">
-        <v>2</v>
+        <v>70.67</v>
       </c>
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A328">
-        <v>276001003238</v>
+        <v>276001005478</v>
       </c>
       <c r="B328" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="C328">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D328">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="E328">
-        <v>8.25</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A329">
-        <v>276001011745</v>
+        <v>176001005058</v>
       </c>
       <c r="B329" t="s">
-        <v>333</v>
+        <v>311</v>
       </c>
       <c r="C329">
-        <v>31</v>
+        <v>100</v>
       </c>
       <c r="D329">
-        <v>15</v>
+        <v>111</v>
       </c>
       <c r="E329">
-        <v>2.0699999999999998</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A330">
-        <v>276001005524</v>
+        <v>176001002962</v>
       </c>
       <c r="B330" t="s">
-        <v>275</v>
+        <v>144</v>
       </c>
       <c r="C330">
-        <v>30</v>
+        <v>392</v>
       </c>
       <c r="D330">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="E330">
-        <v>6</v>
+        <v>4.9000000000000004</v>
       </c>
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A331">
-        <v>276001007659</v>
+        <v>176001022572</v>
       </c>
       <c r="B331" t="s">
-        <v>334</v>
+        <v>159</v>
       </c>
       <c r="C331">
-        <v>28</v>
+        <v>368</v>
       </c>
       <c r="D331">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="E331">
-        <v>2.8</v>
+        <v>9.1999999999999993</v>
       </c>
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A332">
-        <v>276001020434</v>
+        <v>276001011184</v>
       </c>
       <c r="B332" t="s">
-        <v>335</v>
+        <v>250</v>
       </c>
       <c r="C332">
-        <v>28</v>
+        <v>179</v>
       </c>
       <c r="D332">
-        <v>77</v>
+        <v>16</v>
       </c>
       <c r="E332">
-        <v>0.36</v>
+        <v>11.19</v>
       </c>
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A333">
-        <v>276001005478</v>
+        <v>176001012216</v>
       </c>
       <c r="B333" t="s">
-        <v>336</v>
+        <v>177</v>
       </c>
       <c r="C333">
-        <v>24</v>
+        <v>322</v>
       </c>
       <c r="D333">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="E333">
-        <v>0.43</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A334">
-        <v>176001003080</v>
+        <v>276001019193</v>
       </c>
       <c r="B334" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C334">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D334">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E334">
-        <v>1.06</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A335">
-        <v>276001003271</v>
+        <v>176001004507</v>
       </c>
       <c r="B335" t="s">
-        <v>338</v>
+        <v>157</v>
       </c>
       <c r="C335">
-        <v>14</v>
+        <v>371</v>
       </c>
       <c r="D335">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="E335">
-        <v>1.75</v>
+        <v>9.2799999999999994</v>
       </c>
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A336">
-        <v>176001030125</v>
+        <v>176001004663</v>
       </c>
       <c r="B336" t="s">
-        <v>160</v>
+        <v>223</v>
       </c>
       <c r="C336">
-        <v>14</v>
+        <v>230</v>
       </c>
       <c r="D336">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E336">
-        <v>0.7</v>
+        <v>20.91</v>
       </c>
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A337">
-        <v>276001019193</v>
+        <v>376001020501</v>
       </c>
       <c r="B337" t="s">
-        <v>339</v>
+        <v>254</v>
       </c>
       <c r="C337">
-        <v>8</v>
+        <v>174</v>
       </c>
       <c r="D337">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E337">
-        <v>0.38</v>
+        <v>17.399999999999999</v>
       </c>
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A338">
-        <v>276001011753</v>
+        <v>176001025962</v>
       </c>
       <c r="B338" t="s">
-        <v>340</v>
+        <v>119</v>
       </c>
       <c r="C338">
-        <v>7</v>
+        <v>461</v>
       </c>
       <c r="D338">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="E338">
-        <v>0.15</v>
+        <v>6.49</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E338" xr:uid="{00000000-0001-0000-0100-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E338">
+      <sortCondition ref="B1:B338"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
